--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -8258,7 +8258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9515,51 +9515,51 @@
     </row>
     <row r="57">
       <c r="A57" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -9574,17 +9574,17 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9592,24 +9592,24 @@
       <c r="A60" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       <c r="A62" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -9674,17 +9674,17 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -9692,24 +9692,24 @@
       <c r="A64" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9717,24 +9717,24 @@
       <c r="A65" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -9742,9 +9742,9 @@
       <c r="A66" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -9767,24 +9767,24 @@
       <c r="A67" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9792,19 +9792,19 @@
       <c r="A68" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -9842,19 +9842,19 @@
       <c r="A70" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9867,24 +9867,24 @@
       <c r="A71" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -9892,24 +9892,24 @@
       <c r="A72" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9924,12 +9924,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -9942,24 +9942,24 @@
       <c r="A74" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -9967,9 +9967,9 @@
       <c r="A75" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -9992,24 +9992,24 @@
       <c r="A76" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10017,19 +10017,19 @@
       <c r="A77" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -10042,20 +10042,24 @@
       <c r="A78" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr"/>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10063,20 +10067,24 @@
       <c r="A79" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr"/>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10100,12 @@
       <c r="C80" s="7" t="inlineStr"/>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10105,24 +10113,20 @@
       <c r="A81" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10135,19 +10139,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10162,12 +10162,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -10212,12 +10212,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10255,19 +10255,19 @@
       <c r="A87" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -10280,18 +10280,68 @@
       <c r="A88" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="19" t="inlineStr">
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr"/>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr"/>
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -219,10 +219,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8258,7 +8258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8329,16 +8329,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.75</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>26/36</t>
+          <t>27/36</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 18/25 + 交付 8/11 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 18/25 + 交付 9/11 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8361,16 +8361,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>22/44</t>
+          <t>23/44</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 10/24 + 交付 12/20 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 10/24 + 交付 13/20 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8393,29 +8393,29 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.4375</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>21/48</t>
+          <t>22/48</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 9/24 + 交付 12/24 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 9/24 + 交付 13/24 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.7222</v>
+        <v>0.75</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.5</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.4375</v>
+        <v>0.4583</v>
       </c>
     </row>
     <row r="8">
@@ -8462,7 +8462,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>阶段出口清单 — V0 出口  (已打勾 3/8；状态由关联项在当日是否完成/达标推出)</t>
+          <t>阶段出口清单 — V0 出口  (已打勾 4/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>D2 (0/1)</t>
+          <t>D2 (1/1)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -8526,7 +8526,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -8553,7 +8553,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -8580,7 +8580,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8607,7 +8607,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8634,7 +8634,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8661,7 +8661,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8688,7 +8688,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -8749,7 +8749,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8776,7 +8776,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -8803,7 +8803,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -8830,7 +8830,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -8857,7 +8857,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8884,7 +8884,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8911,7 +8911,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8938,7 +8938,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8965,7 +8965,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -8992,7 +8992,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -9019,7 +9019,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -9392,7 +9392,7 @@
       <c r="A52" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
@@ -9565,26 +9565,26 @@
     </row>
     <row r="59">
       <c r="A59" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9592,24 +9592,24 @@
       <c r="A60" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9617,24 +9617,24 @@
       <c r="A61" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9642,9 +9642,9 @@
       <c r="A62" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -9667,9 +9667,9 @@
       <c r="A63" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -9679,12 +9679,12 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -9692,24 +9692,24 @@
       <c r="A64" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -9717,9 +9717,9 @@
       <c r="A65" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9742,24 +9742,24 @@
       <c r="A66" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -9767,9 +9767,9 @@
       <c r="A67" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -9817,24 +9817,24 @@
       <c r="A69" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9842,24 +9842,24 @@
       <c r="A70" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -9867,24 +9867,24 @@
       <c r="A71" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9892,24 +9892,24 @@
       <c r="A72" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -9917,19 +9917,19 @@
       <c r="A73" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -9942,9 +9942,9 @@
       <c r="A74" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9967,24 +9967,24 @@
       <c r="A75" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -9992,9 +9992,9 @@
       <c r="A76" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10017,9 +10017,9 @@
       <c r="A77" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10042,24 +10042,24 @@
       <c r="A78" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10067,24 +10067,24 @@
       <c r="A79" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10097,15 +10097,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr"/>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10113,15 +10117,15 @@
       <c r="A81" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10134,20 +10138,20 @@
       <c r="A82" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10160,19 +10164,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C83" s="7" t="inlineStr"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -10212,12 +10212,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -10287,17 +10287,17 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10305,24 +10305,24 @@
       <c r="A89" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -10330,18 +10330,43 @@
       <c r="A90" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="19" t="inlineStr">
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr"/>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr"/>
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -10489,7 +10514,7 @@
           <t>数据通路</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -10534,7 +10559,7 @@
       <c r="N4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10593,7 +10618,7 @@
       <c r="N5" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10652,7 +10677,7 @@
       <c r="N6" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10711,7 +10736,7 @@
       <c r="N7" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10770,7 +10795,7 @@
       <c r="N8" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10825,7 +10850,7 @@
       </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10882,7 +10907,7 @@
       <c r="N10" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10910,7 +10935,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -10955,7 +10980,7 @@
       <c r="N11" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10983,7 +11008,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11028,7 +11053,7 @@
       <c r="N12" s="6" t="n">
         <v>41472</v>
       </c>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11087,7 +11112,7 @@
       <c r="N13" s="6" t="n">
         <v>605</v>
       </c>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11160,7 +11185,7 @@
       <c r="N14" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11247,7 +11272,7 @@
           <t>几何</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11292,7 +11317,7 @@
       <c r="N16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11351,7 +11376,7 @@
       <c r="N17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11379,7 +11404,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11424,7 +11449,7 @@
       <c r="N18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11497,7 +11522,7 @@
       <c r="N19" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11843,7 +11868,7 @@
       <c r="N25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="12" t="inlineStr">
+      <c r="O25" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -12003,7 +12028,7 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -12048,7 +12073,7 @@
       <c r="N28" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="O28" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -12107,7 +12132,7 @@
       <c r="N29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="O29" s="12" t="inlineStr">
+      <c r="O29" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -12129,7 +12154,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -14946,7 +14971,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -15145,7 +15170,7 @@
       <c r="F25" s="17" t="n">
         <v>46307</v>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15183,7 +15208,7 @@
       <c r="F26" s="17" t="n">
         <v>46307</v>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15221,7 +15246,7 @@
       <c r="F27" s="17" t="n">
         <v>46307</v>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15259,7 +15284,7 @@
       <c r="F28" s="17" t="n">
         <v>46307</v>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15297,7 +15322,7 @@
       <c r="F29" s="17" t="n">
         <v>46307</v>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15335,7 +15360,7 @@
       <c r="F30" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15373,7 +15398,7 @@
       <c r="F31" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15411,7 +15436,7 @@
       <c r="F32" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15446,15 +15471,17 @@
       <c r="E33" s="17" t="n">
         <v>46311</v>
       </c>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F33" s="17" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>上板: 逐字节一致+30 min 无停摆; 帧率 4.2&lt;15 待修 (3ca644e)</t>
+          <t>782e9e3 复验过 (60 min 带载 0 停摆, 15 fps); 合主线中 (M1)</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15512,7 @@
       <c r="F34" s="17" t="n">
         <v>46309</v>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15523,7 +15550,7 @@
       <c r="F35" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15561,7 +15588,7 @@
       <c r="F36" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15599,7 +15626,7 @@
       <c r="F37" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -8258,7 +8258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9590,76 +9590,76 @@
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9667,24 +9667,24 @@
       <c r="A63" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9694,22 +9694,22 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9717,24 +9717,24 @@
       <c r="A65" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -9742,24 +9742,24 @@
       <c r="A66" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -9792,19 +9792,19 @@
       <c r="A68" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -9817,24 +9817,24 @@
       <c r="A69" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -9849,17 +9849,17 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -9867,19 +9867,19 @@
       <c r="A71" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9892,24 +9892,24 @@
       <c r="A72" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9924,17 +9924,17 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -9967,24 +9967,24 @@
       <c r="A75" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -9992,19 +9992,19 @@
       <c r="A76" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -10017,24 +10017,24 @@
       <c r="A77" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10049,17 +10049,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10067,24 +10067,24 @@
       <c r="A79" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10092,24 +10092,24 @@
       <c r="A80" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10117,20 +10117,24 @@
       <c r="A81" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr"/>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10138,20 +10142,24 @@
       <c r="A82" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr"/>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10164,15 +10172,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr"/>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10185,19 +10197,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C84" s="7" t="inlineStr"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10205,24 +10213,20 @@
       <c r="A85" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr"/>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10235,19 +10239,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>D12;D13;D14</t>
-        </is>
-      </c>
+      <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10262,12 +10262,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -10312,17 +10312,17 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10330,19 +10330,19 @@
       <c r="A90" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -10355,18 +10355,93 @@
       <c r="A91" s="17" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="19" t="inlineStr">
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>D15;D16</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr"/>
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -15669,7 +15744,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>7ef55e1 离线 3 遍过; 上板 16/16 过一轮 (旧提交), V3 待补测</t>
+          <t>7ef55e1 离线过; 上板 V3 待补测 (agent 已关, 开新的接)</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15924,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>764f81d; 晚间 WiFi 差两次上板未过, 待主机空闲复测</t>
+          <t>764f81d; 晚间 WiFi 差未过, 主机空闲时主会话复测</t>
         </is>
       </c>
     </row>
@@ -15885,7 +15960,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>9630437 已装板: 复位→亮起 15.8 s / 找板 25.6 s; 余 2 项待用户批准写启动文件 (fdbb217)</t>
+          <t>fdbb217 已装板: 亮起 15.8 s / 找板 25.6 s; 第二步 (写启动文件) 待用户批准</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15996,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>离线复验过 + 用户实转看过 (ffbfeeb, geo 循环 956e1ff); 待正式上板验收</t>
+          <t>离线过 + 用户实转看过 (ffbfeeb); 未合</t>
         </is>
       </c>
     </row>
@@ -15957,7 +16032,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>阶段 1 合主线 1995be8; 阶段 2 待 D2/D12/D13 合并</t>
+          <t>阶段 1 合主线 1995be8; 阶段 2 待 D2 合主线后开新 agent</t>
         </is>
       </c>
     </row>
@@ -15993,7 +16068,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>task/d16-ddr</t>
+          <t>539d303: 根因 = 按角度 DDR 换行 + 负载叠加; 4×4 分块待用户定</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -15,7 +15,7 @@
     <sheet name="历史记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,10 +219,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2421,12 +2427,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$260</f>
+              <f>'指标趋势'!$A$260:$A$261</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$260</f>
+              <f>'指标趋势'!$B$260:$B$261</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2464,12 +2470,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$260</f>
+              <f>'指标趋势'!$A$260:$A$261</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$260</f>
+              <f>'指标趋势'!$C$260:$C$261</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2590,7 +2596,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46309"/>
-          <min val="46307"/>
+          <min val="46308"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2706,12 +2712,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$277:$A$278</f>
+              <f>'指标趋势'!$A$277:$A$279</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$277:$B$278</f>
+              <f>'指标趋势'!$B$277:$B$279</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2749,12 +2755,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$277:$A$278</f>
+              <f>'指标趋势'!$A$277:$A$279</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$C$277:$C$278</f>
+              <f>'指标趋势'!$C$277:$C$279</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -2874,7 +2880,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
+          <max val="46309"/>
           <min val="46307"/>
         </scaling>
         <delete val="0"/>
@@ -3233,12 +3239,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$5:$A$11</f>
+              <f>'指标趋势'!$A$5:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$5:$B$11</f>
+              <f>'指标趋势'!$B$5:$B$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3358,7 +3364,7 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="46308"/>
+          <max val="46309"/>
           <min val="46157"/>
         </scaling>
         <delete val="0"/>
@@ -8258,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8453,119 +8459,139 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>今天没有新的硬件实测值</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>KR1.1</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>持平</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>内容刷新率 (假转, 管线能力) (fps, 越大越好)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>15 (10-13) → 15</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>15 / 12 / 15；dr1v90 task/pls-2047 782e9e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>KR7.1</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>持平</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>丢帧/迟到率 (%, 越小越好)</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>0 (10-13) → 0</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>0.1 / 0.1 / 0.1；dr1v90 task/pls-2047 782e9e3 (主会话上板复验 v4.log)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>KR7.2</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>变好</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>连续无故障: 软件链路 (假转, 无人值守) (h, 越大越好)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>0.17 (10-13) → 1</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>8 / 8 / 24；dr1v90 task/pls-2047 782e9e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>阶段出口清单 — V0 出口  (已打勾 4/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>①2047 PL 切片上板通过</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>D2 (1/1)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>②主机实时推流 15 fps</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>D1 (1/1)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>③几何更正 + 镜像已核实</t>
+          <t>①2047 PL 切片上板通过</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>KR5.2 (1/1)</t>
+          <t>D2 (1/1)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -8577,22 +8603,22 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
+          <t>②主机实时推流 15 fps</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>KR8.1;KR8.2;D13 (0/3)</t>
+          <t>D1 (1/1)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -8604,22 +8630,22 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
+          <t>③几何更正 + 镜像已核实</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>D7;KR9.1;KR9.2 (0/3)</t>
+          <t>KR5.2 (1/1)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -8631,7 +8657,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -8641,12 +8667,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>⑥软件链路无人值守 ≥8 h</t>
+          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>KR7.2 (0/1)</t>
+          <t>KR8.1;KR8.2;D13 (0/3)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -8658,7 +8684,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -8668,12 +8694,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>D15 (0/1)</t>
+          <t>D7;KR9.1;KR9.2 (0/3)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -8685,137 +8711,137 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>⑥软件链路无人值守 ≥8 h</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>KR7.2 (0/1)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>D15 (0/1)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>⑧内容 ≥2 + 一种交互</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>KR10.1;KR10.2 (2/2)</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>阶段出口清单 — V1 回板当天就绪  (已打勾 3/11；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>D10 (0/1)</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>②桥 1 期 6 链 24 Hz 位流</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>D5 (1/1)</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>③桥接收 + 1.2G PRBS 测试件</t>
+          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>D4 (1/1)</t>
+          <t>D10 (0/1)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -8827,22 +8853,22 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>④1 期几何 LUT + 校准工具</t>
+          <t>②桥 1 期 6 链 24 Hz 位流</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>D6 (1/1)</t>
+          <t>D5 (1/1)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -8854,22 +8880,22 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
+          <t>③桥接收 + 1.2G PRBS 测试件</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>D8 (0/1)</t>
+          <t>D4 (1/1)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -8881,22 +8907,22 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>⑥全链路系统仿真</t>
+          <t>④1 期几何 LUT + 校准工具</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>D9 (0/1)</t>
+          <t>D6 (1/1)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -8908,7 +8934,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -8918,12 +8944,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>⑦C1 台架逐像素 0 错</t>
+          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>D11 (0/1)</t>
+          <t>D8 (0/1)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -8935,7 +8961,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -8945,12 +8971,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>⑧整机回板点亮步骤 + 一键脚本</t>
+          <t>⑥全链路系统仿真</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D9 (0/1)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -8962,7 +8988,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -8972,12 +8998,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+          <t>⑦C1 台架逐像素 0 错</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D11 (0/1)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -8989,7 +9015,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -8999,7 +9025,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>⑩面板映射 4 项信息到位</t>
+          <t>⑧整机回板点亮步骤 + 一键脚本</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -9016,1225 +9042,1237 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>⑩面板映射 4 项信息到位</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>⑪无串口运维可用</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>D7 (0/1)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>风险表 (risks.csv；红 = 开，黄 = 监控，绿 = 关)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>影响 / 应对</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>负责 · 登记日期 · 来源</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>1.2G 可能过不了</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
 应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>影响：时钟偏差会丢帧
 应对：退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>影响：每块下半屏黑
 应对：硬件确认并补 0Ω</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>2260 从未收到合法 ACK（疑物理通路）</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>影响：1 期显示可能起不来
 应对：验证板一颗一组针对此问题，回板验证</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>影响：2 期 32 bit 像素带宽不够
 应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>WiFi/主机负载造成延迟尾巴（10-13 晚 p99 334 ms）</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>影响：延迟抖动超标
 应对：演示时停重任务；后续增量帧</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E47" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>影响：高速下接触不良/脱落
 应对：T2 板留 eMMC、打胶</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>D 盘 EIO（IP-guard 驱动）</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>影响：构建/提交偶发失败
 应对：看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>1 期面板映射缺 4 项信息</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>影响：1 期桥表无法定稿
 应对：问硬件同事</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>每日流水 (daily_log.csv，按天倒序)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="17" t="n">
+    <row r="54">
+      <c r="A54" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17" t="n">
+    <row r="55">
+      <c r="A55" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="n">
+    <row r="56">
+      <c r="A56" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="n">
+    <row r="57">
+      <c r="A57" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="n">
+    <row r="58">
+      <c r="A58" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="n">
+    <row r="59">
+      <c r="A59" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="17" t="n">
+    <row r="60">
+      <c r="A60" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="17" t="n">
+    <row r="61">
+      <c r="A61" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="17" t="n">
+    <row r="62">
+      <c r="A62" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>D16</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="17" t="n">
+    <row r="63">
+      <c r="A63" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B63" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="17" t="n">
+    <row r="64">
+      <c r="A64" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="19" t="inlineStr">
+      <c r="B64" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="17" t="n">
+    <row r="65">
+      <c r="A65" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="17" t="n">
+    <row r="66">
+      <c r="A66" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>E7</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="17" t="n">
+    <row r="67">
+      <c r="A67" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>交付完成</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="n">
+    <row r="68">
+      <c r="A68" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="17" t="n">
+    <row r="69">
+      <c r="A69" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="17" t="n">
+    <row r="70">
+      <c r="A70" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="17" t="n">
+    <row r="71">
+      <c r="A71" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="17" t="n">
+    <row r="72">
+      <c r="A72" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="17" t="n">
+    <row r="73">
+      <c r="A73" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="17" t="n">
+    <row r="74">
+      <c r="A74" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="17" t="n">
+    <row r="75">
+      <c r="A75" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="17" t="n">
+    <row r="76">
+      <c r="A76" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="17" t="n">
+    <row r="77">
+      <c r="A77" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>D14</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="17" t="n">
+    <row r="78">
+      <c r="A78" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="17" t="n">
+    <row r="79">
+      <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B79" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="17" t="n">
+    <row r="80">
+      <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="17" t="n">
+    <row r="81">
+      <c r="A81" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
+      <c r="B81" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="17" t="n">
+    <row r="82">
+      <c r="A82" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="19" t="inlineStr">
+      <c r="B82" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="17" t="n">
+    <row r="83">
+      <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B83" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="17" t="n">
+    <row r="84">
+      <c r="A84" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>复验通过</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>D15</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="17" t="n">
+    <row r="85">
+      <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="18" t="inlineStr">
+      <c r="B85" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>D3;D4;D5</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="17" t="n">
+    <row r="86">
+      <c r="A86" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="18" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr"/>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B86" s="18" t="inlineStr">
+      <c r="B86" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
@@ -10242,206 +10280,248 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
           <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="17" t="n">
+    <row r="89">
+      <c r="A89" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="18" t="inlineStr">
+      <c r="B89" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="17" t="n">
+    <row r="90">
+      <c r="A90" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="18" t="inlineStr">
+      <c r="B90" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="17" t="n">
+    <row r="91">
+      <c r="A91" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="18" t="inlineStr">
+      <c r="B91" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>D12;D13;D14</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="17" t="n">
+    <row r="92">
+      <c r="A92" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="18" t="inlineStr">
+      <c r="B92" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>D13</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="17" t="n">
+    <row r="93">
+      <c r="A93" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="18" t="inlineStr">
+      <c r="B93" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>D15;D16</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="17" t="n">
+    <row r="94">
+      <c r="A94" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B92" s="18" t="inlineStr">
+      <c r="B94" s="20" t="inlineStr">
         <is>
           <t>决定</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>KR5.2</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="17" t="n">
+    <row r="95">
+      <c r="A95" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B95" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="n">
+    <row r="96">
+      <c r="A96" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="19" t="inlineStr">
+      <c r="B96" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr"/>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -10482,7 +10562,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>POV3D 显性目的进度看板 — 2026-10-14  (当前期 V0；状态按「最新硬件实测 vs 当前期目标」自动判定，krs.csv 人工状态列可覆盖)</t>
         </is>
@@ -10589,7 +10669,7 @@
           <t>数据通路</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -10617,8 +10697,8 @@
       <c r="I4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="J4" s="17" t="n">
-        <v>46308</v>
+      <c r="J4" s="19" t="n">
+        <v>46309</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
@@ -10634,25 +10714,25 @@
       <c r="N4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191 / 9bf16ad</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="n">
+          <t>dr1v90 task/pls-2047 782e9e3</t>
+        </is>
+      </c>
+      <c r="Q4" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>KR1.2</t>
@@ -10676,7 +10756,7 @@
       <c r="I5" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -10693,7 +10773,7 @@
       <c r="N5" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10703,15 +10783,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q5" s="21" t="n">
+      <c r="Q5" s="23" t="n">
         <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>KR1.7</t>
@@ -10735,7 +10815,7 @@
       <c r="I6" s="6" t="n">
         <v>236.6</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -10752,7 +10832,7 @@
       <c r="N6" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10762,15 +10842,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="n">
+      <c r="Q6" s="23" t="n">
         <v>0.5071851225697379</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>KR1.3</t>
@@ -10794,7 +10874,7 @@
       <c r="I7" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -10811,7 +10891,7 @@
       <c r="N7" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10821,15 +10901,15 @@
           <t>claude_memory/project_m90_wifi_p2p_1012.md</t>
         </is>
       </c>
-      <c r="Q7" s="21" t="n">
+      <c r="Q7" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>KR1.4</t>
@@ -10853,7 +10933,7 @@
       <c r="I8" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -10870,7 +10950,7 @@
       <c r="N8" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10880,15 +10960,15 @@
           <t>dr1v90 9bf16ad</t>
         </is>
       </c>
-      <c r="Q8" s="21" t="n">
+      <c r="Q8" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>KR1.5</t>
@@ -10912,7 +10992,7 @@
       <c r="I9" s="6" t="n">
         <v>17.3</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -10925,7 +11005,7 @@
       </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10935,13 +11015,13 @@
           <t>dr1v90 596b191</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="n"/>
+      <c r="Q9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n"/>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>KR1.6</t>
@@ -10965,7 +11045,7 @@
       <c r="I10" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -10982,7 +11062,7 @@
       <c r="N10" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -10992,7 +11072,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md (D9 首次转起来 640–654 RPM)</t>
         </is>
       </c>
-      <c r="Q10" s="21" t="n">
+      <c r="Q10" s="23" t="n">
         <v>0.7200000000000001</v>
       </c>
     </row>
@@ -11010,7 +11090,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11038,7 +11118,7 @@
       <c r="I11" s="6" t="n">
         <v>21.7</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -11055,7 +11135,7 @@
       <c r="N11" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11065,7 +11145,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q11" s="21" t="n">
+      <c r="Q11" s="23" t="n">
         <v>0.7233333333333333</v>
       </c>
     </row>
@@ -11083,7 +11163,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11111,7 +11191,7 @@
       <c r="I12" s="6" t="n">
         <v>28800</v>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -11128,7 +11208,7 @@
       <c r="N12" s="6" t="n">
         <v>41472</v>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11138,15 +11218,15 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="n">
+      <c r="Q12" s="23" t="n">
         <v>0.6944444444444444</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n"/>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>KR3.2</t>
@@ -11170,7 +11250,7 @@
       <c r="I13" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -11187,7 +11267,7 @@
       <c r="N13" s="6" t="n">
         <v>605</v>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11197,7 +11277,7 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q13" s="21" t="n">
+      <c r="Q13" s="23" t="n">
         <v>0.2347107438016529</v>
       </c>
     </row>
@@ -11215,7 +11295,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>⏸ 无数据 / 未开始</t>
         </is>
@@ -11243,7 +11323,7 @@
       <c r="I14" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -11260,7 +11340,7 @@
       <c r="N14" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O14" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11270,15 +11350,15 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="n">
+      <c r="Q14" s="23" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n"/>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
+      <c r="A15" s="25" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>KR4.2</t>
@@ -11302,7 +11382,7 @@
       <c r="I15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -11319,7 +11399,7 @@
       <c r="N15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="24" t="inlineStr">
+      <c r="O15" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -11329,7 +11409,7 @@
           <t>dr1v90 1995be8 (D15 阶段 1, 主会话复验)</t>
         </is>
       </c>
-      <c r="Q15" s="21" t="n">
+      <c r="Q15" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11347,7 +11427,7 @@
           <t>几何</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11375,7 +11455,7 @@
       <c r="I16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -11392,7 +11472,7 @@
       <c r="N16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11402,15 +11482,15 @@
           <t>dr1v90 44ed2cd</t>
         </is>
       </c>
-      <c r="Q16" s="21" t="n">
+      <c r="Q16" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="n"/>
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
           <t>KR5.2</t>
@@ -11434,7 +11514,7 @@
       <c r="I17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -11451,7 +11531,7 @@
       <c r="N17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11461,7 +11541,7 @@
           <t>dr1v90 49031f6 (VOXSLICE_M90.md 10-13 节)</t>
         </is>
       </c>
-      <c r="Q17" s="21" t="n">
+      <c r="Q17" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11479,7 +11559,7 @@
           <t>显示优化</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -11507,7 +11587,7 @@
       <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -11524,7 +11604,7 @@
       <c r="N18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O18" s="11" t="inlineStr">
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11534,7 +11614,7 @@
           <t>dr1v90 3bc5736</t>
         </is>
       </c>
-      <c r="Q18" s="21" t="n">
+      <c r="Q18" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11552,7 +11632,7 @@
           <t>稳定</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11580,8 +11660,8 @@
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="17" t="n">
-        <v>46308</v>
+      <c r="J19" s="19" t="n">
+        <v>46309</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -11597,25 +11677,25 @@
       <c r="N19" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O19" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
-        </is>
-      </c>
-      <c r="Q19" s="21" t="n">
+          <t>dr1v90 task/pls-2047 782e9e3 (主会话上板复验 v4.log)</t>
+        </is>
+      </c>
+      <c r="Q19" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>KR7.2</t>
@@ -11637,10 +11717,10 @@
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <v>46308</v>
+        <v>1</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>46309</v>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
@@ -11656,25 +11736,25 @@
       <c r="N20" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="O20" s="15" t="inlineStr">
+      <c r="O20" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
-        </is>
-      </c>
-      <c r="Q20" s="21" t="n">
-        <v>0.007083333333333334</v>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
+        </is>
+      </c>
+      <c r="Q20" s="23" t="n">
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="n"/>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>KR7.3</t>
@@ -11696,7 +11776,7 @@
         </is>
       </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="17" t="n"/>
+      <c r="J21" s="19" t="n"/>
       <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="6" t="n">
         <v>1</v>
@@ -11707,13 +11787,13 @@
       <c r="N21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="24" t="inlineStr">
+      <c r="O21" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="21" t="n"/>
+      <c r="Q21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -11729,7 +11809,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11757,7 +11837,7 @@
       <c r="I22" s="6" t="n">
         <v>15.8</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -11774,7 +11854,7 @@
       <c r="N22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="O22" s="15" t="inlineStr">
+      <c r="O22" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11784,15 +11864,15 @@
           <t>dr1v90 task/d13-boot fdbb217 (d13_boot/runs/levers, 串口真实复位时刻)</t>
         </is>
       </c>
-      <c r="Q22" s="21" t="n">
+      <c r="Q22" s="23" t="n">
         <v>0.7594936708860759</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
           <t>KR8.4</t>
@@ -11816,7 +11896,7 @@
       <c r="I23" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -11827,7 +11907,7 @@
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="15" t="inlineStr">
+      <c r="O23" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11837,13 +11917,13 @@
           <t>claude_memory/project_slice_3bit_cpu_trial.md</t>
         </is>
       </c>
-      <c r="Q23" s="21" t="n"/>
+      <c r="Q23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>KR8.2</t>
@@ -11867,7 +11947,7 @@
       <c r="I24" s="6" t="n">
         <v>25.6</v>
       </c>
-      <c r="J24" s="17" t="n">
+      <c r="J24" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -11884,7 +11964,7 @@
       <c r="N24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="O24" s="15" t="inlineStr">
+      <c r="O24" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11894,15 +11974,15 @@
           <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
-      <c r="Q24" s="21" t="n">
+      <c r="Q24" s="23" t="n">
         <v>0.78125</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="n"/>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
           <t>KR8.3</t>
@@ -11926,7 +12006,7 @@
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="19" t="n">
         <v>46307</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -11943,7 +12023,7 @@
       <c r="N25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="11" t="inlineStr">
+      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11953,7 +12033,7 @@
           <t>dr1v90 30d82f9</t>
         </is>
       </c>
-      <c r="Q25" s="21" t="n">
+      <c r="Q25" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11971,7 +12051,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11999,7 +12079,7 @@
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J26" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -12016,7 +12096,7 @@
       <c r="N26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="15" t="inlineStr">
+      <c r="O26" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12026,15 +12106,15 @@
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="Q26" s="21" t="n">
+      <c r="Q26" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="n"/>
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>KR9.2</t>
@@ -12058,7 +12138,7 @@
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -12075,7 +12155,7 @@
       <c r="N27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="15" t="inlineStr">
+      <c r="O27" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12085,7 +12165,7 @@
           <t>dr1v90 task/rotor-ops 05c4231</t>
         </is>
       </c>
-      <c r="Q27" s="21" t="n">
+      <c r="Q27" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12103,7 +12183,7 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>✅ 达成当前期目标</t>
         </is>
@@ -12131,7 +12211,7 @@
       <c r="I28" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -12148,7 +12228,7 @@
       <c r="N28" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="O28" s="11" t="inlineStr">
+      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -12158,15 +12238,15 @@
           <t>dr1v90 task/d14-content ffbfeeb + 用户实转观看</t>
         </is>
       </c>
-      <c r="Q28" s="21" t="n">
+      <c r="Q28" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="n"/>
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>KR10.2</t>
@@ -12190,7 +12270,7 @@
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="17" t="n">
+      <c r="J29" s="19" t="n">
         <v>46308</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -12207,7 +12287,7 @@
       <c r="N29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="O29" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -12217,60 +12297,60 @@
           <t>dr1v90 live_push/README.md</t>
         </is>
       </c>
-      <c r="Q29" s="21" t="n">
+      <c r="Q29" s="23" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>达成当前期目标</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>进行中 / 未达标</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>无数据 / 未开始</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>退步 / 阻塞</t>
         </is>
@@ -12342,54 +12422,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>KR1.1 内容刷新率 (假转, 管线能力) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G4" s="28" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H4" s="28" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I4" s="28" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12431,19 +12511,19 @@
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>12</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>15</v>
@@ -12494,55 +12574,64 @@
       </c>
       <c r="C11" s="6" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>KR1.2 端到端延迟 p50 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I21" s="28" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12596,54 +12685,54 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>KR1.7 端到端延迟抖动 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F38" s="28" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G38" s="28" t="inlineStr">
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12697,54 +12786,54 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>KR1.3 WiFi 可用带宽 (Mbit/s, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28" t="inlineStr">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B55" s="28" t="inlineStr">
+      <c r="B55" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C55" s="28" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D55" s="28" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E55" s="28" t="inlineStr">
+      <c r="E55" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F55" s="28" t="inlineStr">
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G55" s="28" t="inlineStr">
+      <c r="G55" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H55" s="28" t="inlineStr">
+      <c r="H55" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I55" s="28" t="inlineStr">
+      <c r="I55" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12832,54 +12921,54 @@
       <c r="C60" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>KR1.4 主机出帧耗时 p99 (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="28" t="inlineStr">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B72" s="28" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C72" s="28" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D72" s="28" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E72" s="28" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F72" s="28" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G72" s="28" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H72" s="28" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I72" s="28" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -12940,34 +13029,34 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27" t="inlineStr">
+      <c r="A88" s="29" t="inlineStr">
         <is>
           <t>KR1.5 板上切片耗时 (每帧) (ms, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="28" t="inlineStr">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B89" s="28" t="inlineStr">
+      <c r="B89" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C89" s="28" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D89" s="28" t="inlineStr">
+      <c r="D89" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E89" s="28" t="inlineStr">
+      <c r="E89" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
@@ -13004,54 +13093,54 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="27" t="inlineStr">
+      <c r="A105" s="29" t="inlineStr">
         <is>
           <t>KR1.6 内容刷新率 (实转上屏) (fps, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="28" t="inlineStr">
+      <c r="A106" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B106" s="28" t="inlineStr">
+      <c r="B106" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C106" s="28" t="inlineStr">
+      <c r="C106" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D106" s="28" t="inlineStr">
+      <c r="D106" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E106" s="28" t="inlineStr">
+      <c r="E106" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F106" s="28" t="inlineStr">
+      <c r="F106" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G106" s="28" t="inlineStr">
+      <c r="G106" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H106" s="28" t="inlineStr">
+      <c r="H106" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I106" s="28" t="inlineStr">
+      <c r="I106" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13105,54 +13194,54 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="27" t="inlineStr">
+      <c r="A122" s="29" t="inlineStr">
         <is>
           <t>KR2.1 体帧率 (Hz, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="28" t="inlineStr">
+      <c r="A123" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B123" s="28" t="inlineStr">
+      <c r="B123" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C123" s="28" t="inlineStr">
+      <c r="C123" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D123" s="28" t="inlineStr">
+      <c r="D123" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E123" s="28" t="inlineStr">
+      <c r="E123" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F123" s="28" t="inlineStr">
+      <c r="F123" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G123" s="28" t="inlineStr">
+      <c r="G123" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H123" s="28" t="inlineStr">
+      <c r="H123" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I123" s="28" t="inlineStr">
+      <c r="I123" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13222,54 +13311,54 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="27" t="inlineStr">
+      <c r="A139" s="29" t="inlineStr">
         <is>
           <t>KR3.1 每面像素数 (px, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="28" t="inlineStr">
+      <c r="A140" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B140" s="28" t="inlineStr">
+      <c r="B140" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C140" s="28" t="inlineStr">
+      <c r="C140" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D140" s="28" t="inlineStr">
+      <c r="D140" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E140" s="28" t="inlineStr">
+      <c r="E140" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F140" s="28" t="inlineStr">
+      <c r="F140" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G140" s="28" t="inlineStr">
+      <c r="G140" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H140" s="28" t="inlineStr">
+      <c r="H140" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I140" s="28" t="inlineStr">
+      <c r="I140" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13330,54 +13419,54 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="27" t="inlineStr">
+      <c r="A156" s="29" t="inlineStr">
         <is>
           <t>KR3.2 每圈片数 (片, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="28" t="inlineStr">
+      <c r="A157" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B157" s="28" t="inlineStr">
+      <c r="B157" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C157" s="28" t="inlineStr">
+      <c r="C157" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D157" s="28" t="inlineStr">
+      <c r="D157" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E157" s="28" t="inlineStr">
+      <c r="E157" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F157" s="28" t="inlineStr">
+      <c r="F157" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G157" s="28" t="inlineStr">
+      <c r="G157" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H157" s="28" t="inlineStr">
+      <c r="H157" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I157" s="28" t="inlineStr">
+      <c r="I157" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13456,54 +13545,54 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="27" t="inlineStr">
+      <c r="A173" s="29" t="inlineStr">
         <is>
           <t>KR4.1 色深 (bit/通道, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="28" t="inlineStr">
+      <c r="A174" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B174" s="28" t="inlineStr">
+      <c r="B174" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C174" s="28" t="inlineStr">
+      <c r="C174" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D174" s="28" t="inlineStr">
+      <c r="D174" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E174" s="28" t="inlineStr">
+      <c r="E174" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F174" s="28" t="inlineStr">
+      <c r="F174" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G174" s="28" t="inlineStr">
+      <c r="G174" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H174" s="28" t="inlineStr">
+      <c r="H174" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I174" s="28" t="inlineStr">
+      <c r="I174" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13591,54 +13680,54 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="27" t="inlineStr">
+      <c r="A190" s="29" t="inlineStr">
         <is>
           <t>KR4.2 链路色深 12-bit 已验证 (1=是) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="28" t="inlineStr">
+      <c r="A191" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B191" s="28" t="inlineStr">
+      <c r="B191" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C191" s="28" t="inlineStr">
+      <c r="C191" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D191" s="28" t="inlineStr">
+      <c r="D191" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E191" s="28" t="inlineStr">
+      <c r="E191" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F191" s="28" t="inlineStr">
+      <c r="F191" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G191" s="28" t="inlineStr">
+      <c r="G191" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H191" s="28" t="inlineStr">
+      <c r="H191" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I191" s="28" t="inlineStr">
+      <c r="I191" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13692,54 +13781,54 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="27" t="inlineStr">
+      <c r="A207" s="29" t="inlineStr">
         <is>
           <t>KR5.1 几何 LUT 复现正确 (1=逐字节复现) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="28" t="inlineStr">
+      <c r="A208" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B208" s="28" t="inlineStr">
+      <c r="B208" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C208" s="28" t="inlineStr">
+      <c r="C208" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D208" s="28" t="inlineStr">
+      <c r="D208" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E208" s="28" t="inlineStr">
+      <c r="E208" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F208" s="28" t="inlineStr">
+      <c r="F208" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G208" s="28" t="inlineStr">
+      <c r="G208" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H208" s="28" t="inlineStr">
+      <c r="H208" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I208" s="28" t="inlineStr">
+      <c r="I208" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13800,54 +13889,54 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="27" t="inlineStr">
+      <c r="A224" s="29" t="inlineStr">
         <is>
           <t>KR5.2 左右镜像已核实 (1=已核) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="28" t="inlineStr">
+      <c r="A225" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B225" s="28" t="inlineStr">
+      <c r="B225" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C225" s="28" t="inlineStr">
+      <c r="C225" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D225" s="28" t="inlineStr">
+      <c r="D225" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E225" s="28" t="inlineStr">
+      <c r="E225" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F225" s="28" t="inlineStr">
+      <c r="F225" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G225" s="28" t="inlineStr">
+      <c r="G225" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H225" s="28" t="inlineStr">
+      <c r="H225" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I225" s="28" t="inlineStr">
+      <c r="I225" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -13901,54 +13990,54 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="27" t="inlineStr">
+      <c r="A241" s="29" t="inlineStr">
         <is>
           <t>KR6.1 停转自动低亮 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="28" t="inlineStr">
+      <c r="A242" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B242" s="28" t="inlineStr">
+      <c r="B242" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C242" s="28" t="inlineStr">
+      <c r="C242" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D242" s="28" t="inlineStr">
+      <c r="D242" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E242" s="28" t="inlineStr">
+      <c r="E242" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F242" s="28" t="inlineStr">
+      <c r="F242" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G242" s="28" t="inlineStr">
+      <c r="G242" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H242" s="28" t="inlineStr">
+      <c r="H242" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I242" s="28" t="inlineStr">
+      <c r="I242" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14002,54 +14091,54 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="27" t="inlineStr">
+      <c r="A258" s="29" t="inlineStr">
         <is>
           <t>KR7.1 丢帧/迟到率 (%, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="28" t="inlineStr">
+      <c r="A259" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B259" s="28" t="inlineStr">
+      <c r="B259" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C259" s="28" t="inlineStr">
+      <c r="C259" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D259" s="28" t="inlineStr">
+      <c r="D259" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E259" s="28" t="inlineStr">
+      <c r="E259" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F259" s="28" t="inlineStr">
+      <c r="F259" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G259" s="28" t="inlineStr">
+      <c r="G259" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H259" s="28" t="inlineStr">
+      <c r="H259" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I259" s="28" t="inlineStr">
+      <c r="I259" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14066,25 +14155,32 @@
         <v>0</v>
       </c>
       <c r="D260" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E260" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F260" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="H260" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I260" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="261">
+      <c r="A261" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B261" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" s="6" t="n"/>
       <c r="D261" s="8" t="n">
         <v>46309</v>
       </c>
@@ -14105,54 +14201,54 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="27" t="inlineStr">
+      <c r="A275" s="29" t="inlineStr">
         <is>
           <t>KR7.2 连续无故障: 软件链路 (假转, 无人值守) (h, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="28" t="inlineStr">
+      <c r="A276" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B276" s="28" t="inlineStr">
+      <c r="B276" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C276" s="28" t="inlineStr">
+      <c r="C276" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D276" s="28" t="inlineStr">
+      <c r="D276" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E276" s="28" t="inlineStr">
+      <c r="E276" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F276" s="28" t="inlineStr">
+      <c r="F276" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G276" s="28" t="inlineStr">
+      <c r="G276" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H276" s="28" t="inlineStr">
+      <c r="H276" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I276" s="28" t="inlineStr">
+      <c r="I276" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14194,73 +14290,82 @@
       </c>
       <c r="C278" s="6" t="n"/>
       <c r="D278" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E278" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F278" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>8</v>
       </c>
       <c r="H278" s="8" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I278" s="6" t="n">
         <v>24</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" s="6" t="n"/>
+    </row>
     <row r="292">
-      <c r="A292" s="27" t="inlineStr">
+      <c r="A292" s="29" t="inlineStr">
         <is>
           <t>KR8.1 上电到 0° 片亮起 (停转) (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="28" t="inlineStr">
+      <c r="A293" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B293" s="28" t="inlineStr">
+      <c r="B293" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C293" s="28" t="inlineStr">
+      <c r="C293" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D293" s="28" t="inlineStr">
+      <c r="D293" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E293" s="28" t="inlineStr">
+      <c r="E293" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F293" s="28" t="inlineStr">
+      <c r="F293" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G293" s="28" t="inlineStr">
+      <c r="G293" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H293" s="28" t="inlineStr">
+      <c r="H293" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I293" s="28" t="inlineStr">
+      <c r="I293" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14314,24 +14419,24 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="27" t="inlineStr">
+      <c r="A309" s="29" t="inlineStr">
         <is>
           <t>KR8.4 上电到转稳全亮 (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="28" t="inlineStr">
+      <c r="A310" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B310" s="28" t="inlineStr">
+      <c r="B310" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C310" s="28" t="inlineStr">
+      <c r="C310" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
@@ -14347,54 +14452,54 @@
       <c r="C311" s="6" t="n"/>
     </row>
     <row r="326">
-      <c r="A326" s="27" t="inlineStr">
+      <c r="A326" s="29" t="inlineStr">
         <is>
           <t>KR8.2 按名字找到板子 (s, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="28" t="inlineStr">
+      <c r="A327" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B327" s="28" t="inlineStr">
+      <c r="B327" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C327" s="28" t="inlineStr">
+      <c r="C327" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D327" s="28" t="inlineStr">
+      <c r="D327" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E327" s="28" t="inlineStr">
+      <c r="E327" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F327" s="28" t="inlineStr">
+      <c r="F327" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G327" s="28" t="inlineStr">
+      <c r="G327" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H327" s="28" t="inlineStr">
+      <c r="H327" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I327" s="28" t="inlineStr">
+      <c r="I327" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14448,54 +14553,54 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="27" t="inlineStr">
+      <c r="A343" s="29" t="inlineStr">
         <is>
           <t>KR8.3 需要串口 (1=需要) (是/否, 越小越好)</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="28" t="inlineStr">
+      <c r="A344" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B344" s="28" t="inlineStr">
+      <c r="B344" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C344" s="28" t="inlineStr">
+      <c r="C344" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D344" s="28" t="inlineStr">
+      <c r="D344" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E344" s="28" t="inlineStr">
+      <c r="E344" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F344" s="28" t="inlineStr">
+      <c r="F344" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G344" s="28" t="inlineStr">
+      <c r="G344" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H344" s="28" t="inlineStr">
+      <c r="H344" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I344" s="28" t="inlineStr">
+      <c r="I344" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14549,54 +14654,54 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="27" t="inlineStr">
+      <c r="A360" s="29" t="inlineStr">
         <is>
           <t>KR9.1 转子遥测可用 (1=可用) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="28" t="inlineStr">
+      <c r="A361" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B361" s="28" t="inlineStr">
+      <c r="B361" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C361" s="28" t="inlineStr">
+      <c r="C361" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D361" s="28" t="inlineStr">
+      <c r="D361" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E361" s="28" t="inlineStr">
+      <c r="E361" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F361" s="28" t="inlineStr">
+      <c r="F361" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G361" s="28" t="inlineStr">
+      <c r="G361" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H361" s="28" t="inlineStr">
+      <c r="H361" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I361" s="28" t="inlineStr">
+      <c r="I361" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14650,54 +14755,54 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="27" t="inlineStr">
+      <c r="A377" s="29" t="inlineStr">
         <is>
           <t>KR9.2 远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="28" t="inlineStr">
+      <c r="A378" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B378" s="28" t="inlineStr">
+      <c r="B378" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C378" s="28" t="inlineStr">
+      <c r="C378" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D378" s="28" t="inlineStr">
+      <c r="D378" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E378" s="28" t="inlineStr">
+      <c r="E378" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F378" s="28" t="inlineStr">
+      <c r="F378" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G378" s="28" t="inlineStr">
+      <c r="G378" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H378" s="28" t="inlineStr">
+      <c r="H378" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I378" s="28" t="inlineStr">
+      <c r="I378" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14751,54 +14856,54 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="27" t="inlineStr">
+      <c r="A394" s="29" t="inlineStr">
         <is>
           <t>KR10.1 可实时播放内容数 (个, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="28" t="inlineStr">
+      <c r="A395" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B395" s="28" t="inlineStr">
+      <c r="B395" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C395" s="28" t="inlineStr">
+      <c r="C395" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D395" s="28" t="inlineStr">
+      <c r="D395" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E395" s="28" t="inlineStr">
+      <c r="E395" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F395" s="28" t="inlineStr">
+      <c r="F395" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G395" s="28" t="inlineStr">
+      <c r="G395" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H395" s="28" t="inlineStr">
+      <c r="H395" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I395" s="28" t="inlineStr">
+      <c r="I395" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -14854,54 +14959,54 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="27" t="inlineStr">
+      <c r="A411" s="29" t="inlineStr">
         <is>
           <t>KR10.2 交互方式数 (种, 越大越好)</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="28" t="inlineStr">
+      <c r="A412" s="30" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B412" s="28" t="inlineStr">
+      <c r="B412" s="30" t="inlineStr">
         <is>
           <t>实测</t>
         </is>
       </c>
-      <c r="C412" s="28" t="inlineStr">
+      <c r="C412" s="30" t="inlineStr">
         <is>
           <t>仿真/台架</t>
         </is>
       </c>
-      <c r="D412" s="28" t="inlineStr">
+      <c r="D412" s="30" t="inlineStr">
         <is>
           <t>V0 目标 日期</t>
         </is>
       </c>
-      <c r="E412" s="28" t="inlineStr">
+      <c r="E412" s="30" t="inlineStr">
         <is>
           <t>V0 目标</t>
         </is>
       </c>
-      <c r="F412" s="28" t="inlineStr">
+      <c r="F412" s="30" t="inlineStr">
         <is>
           <t>V1 目标 日期</t>
         </is>
       </c>
-      <c r="G412" s="28" t="inlineStr">
+      <c r="G412" s="30" t="inlineStr">
         <is>
           <t>V1 目标</t>
         </is>
       </c>
-      <c r="H412" s="28" t="inlineStr">
+      <c r="H412" s="30" t="inlineStr">
         <is>
           <t>V2 目标 日期</t>
         </is>
       </c>
-      <c r="I412" s="28" t="inlineStr">
+      <c r="I412" s="30" t="inlineStr">
         <is>
           <t>V2 目标</t>
         </is>
@@ -15239,13 +15344,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15277,13 +15382,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15315,13 +15420,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15353,13 +15458,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15391,13 +15496,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15429,13 +15534,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15467,13 +15572,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15505,13 +15610,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15543,13 +15648,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E33" s="17" t="n">
+      <c r="E33" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15581,13 +15686,13 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15619,13 +15724,13 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15657,13 +15762,13 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15695,13 +15800,13 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E37" s="19" t="n">
         <v>46310</v>
       </c>
-      <c r="F37" s="17" t="n">
+      <c r="F37" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -15733,11 +15838,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15769,11 +15874,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E39" s="17" t="n">
+      <c r="E39" s="19" t="n">
         <v>46315</v>
       </c>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="24" t="inlineStr">
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15805,11 +15910,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="19" t="n">
         <v>46317</v>
       </c>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="24" t="inlineStr">
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15841,11 +15946,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E41" s="17" t="n">
+      <c r="E41" s="19" t="n">
         <v>46317</v>
       </c>
-      <c r="F41" s="17" t="n"/>
-      <c r="G41" s="24" t="inlineStr">
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15877,11 +15982,11 @@
           <t>2260</t>
         </is>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E42" s="19" t="n">
         <v>46319</v>
       </c>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="24" t="inlineStr">
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -15913,11 +16018,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E43" s="17" t="n">
+      <c r="E43" s="19" t="n">
         <v>46310</v>
       </c>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15949,11 +16054,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="15" t="inlineStr">
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -15985,11 +16090,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F45" s="17" t="n"/>
-      <c r="G45" s="15" t="inlineStr">
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16021,11 +16126,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="15" t="inlineStr">
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16057,11 +16162,11 @@
           <t>公共</t>
         </is>
       </c>
-      <c r="E47" s="17" t="n">
+      <c r="E47" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="15" t="inlineStr">
+      <c r="F47" s="19" t="n"/>
+      <c r="G47" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16093,9 +16198,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="24" t="inlineStr">
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16127,9 +16232,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="24" t="inlineStr">
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="19" t="n"/>
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16161,9 +16266,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E50" s="17" t="n"/>
-      <c r="F50" s="17" t="n"/>
-      <c r="G50" s="24" t="inlineStr">
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="19" t="n"/>
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16195,9 +16300,9 @@
           <t>2期</t>
         </is>
       </c>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="17" t="n"/>
-      <c r="G51" s="24" t="inlineStr">
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>⏸</t>
         </is>
@@ -16283,48 +16388,48 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>46317</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <v>46319</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="19" t="n">
         <v>46336</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="19" t="n">
         <v>46338</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="19" t="n">
         <v>46343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>对角线 (y = x)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="31" t="n">
         <v>46308</v>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="31" t="n">
         <v>46308</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="31" t="n">
         <v>46343</v>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="31" t="n">
         <v>46343</v>
       </c>
     </row>
@@ -16340,7 +16445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16402,7 +16507,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="n">
+      <c r="A2" s="31" t="n">
         <v>46157</v>
       </c>
       <c r="B2" s="7" t="n">
@@ -16443,7 +16548,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="n">
+      <c r="A3" s="31" t="n">
         <v>46157</v>
       </c>
       <c r="B3" s="7" t="n">
@@ -16484,7 +16589,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="n">
+      <c r="A4" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B4" s="7" t="n">
@@ -16525,7 +16630,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n">
+      <c r="A5" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B5" s="7" t="n">
@@ -16566,7 +16671,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B6" s="7" t="n">
@@ -16607,7 +16712,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="31" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="7" t="n">
@@ -16648,7 +16753,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="31" t="n">
         <v>46238</v>
       </c>
       <c r="B8" s="7" t="n">
@@ -16689,7 +16794,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="31" t="n">
         <v>46238</v>
       </c>
       <c r="B9" s="7" t="n">
@@ -16730,7 +16835,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="31" t="n">
         <v>46239</v>
       </c>
       <c r="B10" s="7" t="n">
@@ -16771,7 +16876,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="31" t="n">
         <v>46240</v>
       </c>
       <c r="B11" s="7" t="n">
@@ -16812,7 +16917,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="31" t="n">
         <v>46254</v>
       </c>
       <c r="B12" s="7" t="n">
@@ -16853,7 +16958,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="31" t="n">
         <v>46259</v>
       </c>
       <c r="B13" s="7" t="n">
@@ -16894,7 +16999,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="31" t="n">
         <v>46260</v>
       </c>
       <c r="B14" s="7" t="n">
@@ -16935,7 +17040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n">
+      <c r="A15" s="31" t="n">
         <v>46267</v>
       </c>
       <c r="B15" s="7" t="n">
@@ -16976,7 +17081,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n">
+      <c r="A16" s="31" t="n">
         <v>46279</v>
       </c>
       <c r="B16" s="7" t="n">
@@ -17017,7 +17122,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n">
+      <c r="A17" s="31" t="n">
         <v>46280</v>
       </c>
       <c r="B17" s="7" t="n">
@@ -17058,7 +17163,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="31" t="n">
         <v>46280</v>
       </c>
       <c r="B18" s="7" t="n">
@@ -17099,7 +17204,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n">
+      <c r="A19" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B19" s="7" t="n">
@@ -17140,7 +17245,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B20" s="7" t="n">
@@ -17181,7 +17286,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n">
+      <c r="A21" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B21" s="7" t="n">
@@ -17222,7 +17327,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B22" s="7" t="n">
@@ -17263,7 +17368,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n">
+      <c r="A23" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B23" s="7" t="n">
@@ -17304,7 +17409,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B24" s="7" t="n">
@@ -17345,7 +17450,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B25" s="7" t="n">
@@ -17386,7 +17491,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B26" s="7" t="n">
@@ -17427,7 +17532,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B27" s="7" t="n">
@@ -17468,7 +17573,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B28" s="7" t="n">
@@ -17509,7 +17614,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B29" s="7" t="n">
@@ -17550,7 +17655,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="n">
+      <c r="A30" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B30" s="7" t="n">
@@ -17591,7 +17696,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B31" s="7" t="n">
@@ -17632,7 +17737,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="n">
+      <c r="A32" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B32" s="7" t="n">
@@ -17673,7 +17778,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="31" t="n">
         <v>46307</v>
       </c>
       <c r="B33" s="7" t="n">
@@ -17714,7 +17819,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B34" s="7" t="n">
@@ -17755,7 +17860,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B35" s="7" t="n">
@@ -17796,7 +17901,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B36" s="7" t="n">
@@ -17837,7 +17942,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B37" s="7" t="n">
@@ -17878,7 +17983,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B38" s="7" t="n">
@@ -17919,7 +18024,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n">
+      <c r="A39" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B39" s="7" t="n">
@@ -17960,7 +18065,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="n">
+      <c r="A40" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B40" s="7" t="n">
@@ -18001,7 +18106,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n">
+      <c r="A41" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B41" s="7" t="n">
@@ -18042,7 +18147,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="n">
+      <c r="A42" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B42" s="7" t="n">
@@ -18083,7 +18188,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n">
+      <c r="A43" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B43" s="7" t="n">
@@ -18124,7 +18229,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="n">
+      <c r="A44" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B44" s="7" t="n">
@@ -18165,7 +18270,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="n">
+      <c r="A45" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B45" s="7" t="n">
@@ -18206,7 +18311,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="n">
+      <c r="A46" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B46" s="7" t="n">
@@ -18247,7 +18352,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="n">
+      <c r="A47" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B47" s="7" t="n">
@@ -18288,7 +18393,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="n">
+      <c r="A48" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B48" s="7" t="n">
@@ -18329,7 +18434,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="n">
+      <c r="A49" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B49" s="7" t="n">
@@ -18370,7 +18475,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="n">
+      <c r="A50" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B50" s="7" t="n">
@@ -18411,7 +18516,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="n">
+      <c r="A51" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B51" s="7" t="n">
@@ -18452,7 +18557,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="n">
+      <c r="A52" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B52" s="7" t="n">
@@ -18493,7 +18598,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="n">
+      <c r="A53" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B53" s="7" t="n">
@@ -18534,7 +18639,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="n">
+      <c r="A54" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B54" s="7" t="n">
@@ -18575,7 +18680,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="n">
+      <c r="A55" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B55" s="7" t="n">
@@ -18616,7 +18721,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="n">
+      <c r="A56" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B56" s="7" t="n">
@@ -18657,7 +18762,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="n">
+      <c r="A57" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B57" s="7" t="n">
@@ -18698,7 +18803,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="n">
+      <c r="A58" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B58" s="7" t="n">
@@ -18739,7 +18844,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="n">
+      <c r="A59" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B59" s="7" t="n">
@@ -18780,7 +18885,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="n">
+      <c r="A60" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B60" s="7" t="n">
@@ -18821,7 +18926,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="n">
+      <c r="A61" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B61" s="7" t="n">
@@ -18862,7 +18967,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="n">
+      <c r="A62" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B62" s="7" t="n">
@@ -18903,7 +19008,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="n">
+      <c r="A63" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B63" s="7" t="n">
@@ -18944,7 +19049,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="n">
+      <c r="A64" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B64" s="7" t="n">
@@ -18985,7 +19090,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="n">
+      <c r="A65" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B65" s="7" t="n">
@@ -19026,7 +19131,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="n">
+      <c r="A66" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B66" s="7" t="n">
@@ -19067,7 +19172,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="n">
+      <c r="A67" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="B67" s="7" t="n">
@@ -19107,8 +19212,131 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>KR1.1</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>内容刷新率 (假转, 管线能力)</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>fps</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>PL 切片模式假转换网格 15.0/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>KR7.1</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>丢帧/迟到率</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 task/pls-2047 782e9e3 (主会话上板复验 v4.log)</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>2047 PL 切片 60 min 带载: late 0 / miss 0 (按片); drop 为显示自身跳角, 不计</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>KR7.2</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>连续无故障: 软件链路 (假转, 无人值守)</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>假转无人值守带载连续 60 min 无停摆无错 (目标 8 h, 未达)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -8264,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9745,7 +9745,7 @@
     </row>
     <row r="65">
       <c r="A65" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
@@ -9754,17 +9754,17 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -9779,17 +9779,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9804,17 +9804,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9822,9 +9822,9 @@
       <c r="A68" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -9847,9 +9847,9 @@
       <c r="A69" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -9872,24 +9872,24 @@
       <c r="A70" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -9897,9 +9897,9 @@
       <c r="A71" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -9909,12 +9909,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9929,17 +9929,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -9947,9 +9947,9 @@
       <c r="A73" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -9997,24 +9997,24 @@
       <c r="A75" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10022,24 +10022,24 @@
       <c r="A76" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10047,24 +10047,24 @@
       <c r="A77" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10079,17 +10079,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10097,19 +10097,19 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -10122,9 +10122,9 @@
       <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10147,24 +10147,24 @@
       <c r="A81" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10172,9 +10172,9 @@
       <c r="A82" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10197,9 +10197,9 @@
       <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10222,24 +10222,24 @@
       <c r="A84" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10247,24 +10247,24 @@
       <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10277,15 +10277,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr"/>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10293,15 +10297,15 @@
       <c r="A87" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr"/>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -10314,20 +10318,20 @@
       <c r="A88" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B88" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10340,19 +10344,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C89" s="7" t="inlineStr"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10367,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -10467,17 +10467,17 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10485,24 +10485,24 @@
       <c r="A95" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -10510,18 +10510,43 @@
       <c r="A96" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B96" s="21" t="inlineStr">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr"/>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -15661,7 +15686,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>782e9e3 复验过 (60 min 带载 0 停摆, 15 fps); 合主线中 (M1)</t>
+          <t>合主线 2364e5c (782e9e3; M1 解冲突 + 回归, 主会话复核)</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -8264,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8335,16 +8335,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>27/36</t>
+          <t>27/37</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 18/25 + 交付 9/11 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 18/25 + 交付 9/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5227272727272727</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>23/44</t>
+          <t>23/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 10/24 + 交付 13/20 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 10/24 + 交付 13/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8399,29 +8399,29 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4489795918367347</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>22/48</t>
+          <t>22/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 9/24 + 交付 13/24 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 9/24 + 交付 13/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.75</v>
+        <v>0.7297</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5111</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.4583</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="8">
@@ -9770,51 +9770,51 @@
     </row>
     <row r="66">
       <c r="A66" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B66" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -9829,17 +9829,17 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9847,24 +9847,24 @@
       <c r="A69" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -9897,24 +9897,24 @@
       <c r="A71" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -9929,17 +9929,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -9947,24 +9947,24 @@
       <c r="A73" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -9972,24 +9972,24 @@
       <c r="A74" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -9997,9 +9997,9 @@
       <c r="A75" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10022,24 +10022,24 @@
       <c r="A76" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10047,19 +10047,19 @@
       <c r="A77" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -10079,17 +10079,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10097,19 +10097,19 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -10122,24 +10122,24 @@
       <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10147,24 +10147,24 @@
       <c r="A81" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10179,12 +10179,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -10197,24 +10197,24 @@
       <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10222,9 +10222,9 @@
       <c r="A84" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -10247,24 +10247,24 @@
       <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10272,19 +10272,19 @@
       <c r="A86" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B86" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -10297,20 +10297,24 @@
       <c r="A87" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr"/>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10318,20 +10322,24 @@
       <c r="A88" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr"/>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10347,12 +10355,12 @@
       <c r="C89" s="7" t="inlineStr"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10360,24 +10368,20 @@
       <c r="A90" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B90" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10390,19 +10394,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C91" s="7" t="inlineStr"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -10492,17 +10492,17 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10510,19 +10510,19 @@
       <c r="A96" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -10535,18 +10535,68 @@
       <c r="A97" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="21" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -15098,7 +15148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15142,7 +15192,7 @@
         <v>46307</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>5</v>
@@ -15156,7 +15206,7 @@
         <v>46308</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>7</v>
@@ -15170,7 +15220,7 @@
         <v>46309</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>8</v>
@@ -15184,7 +15234,7 @@
         <v>46310</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>10</v>
@@ -15196,10 +15246,10 @@
         <v>46311</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="6" t="n"/>
     </row>
@@ -15208,10 +15258,10 @@
         <v>46312</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="6" t="n"/>
     </row>
@@ -15220,10 +15270,10 @@
         <v>46313</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6" t="n"/>
     </row>
@@ -15232,10 +15282,10 @@
         <v>46314</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="n"/>
     </row>
@@ -15244,10 +15294,10 @@
         <v>46315</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="6" t="n"/>
     </row>
@@ -15256,10 +15306,10 @@
         <v>46316</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="6" t="n"/>
     </row>
@@ -15268,10 +15318,10 @@
         <v>46317</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6" t="n"/>
     </row>
@@ -15280,10 +15330,10 @@
         <v>46318</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="6" t="n"/>
     </row>
@@ -15292,10 +15342,10 @@
         <v>46319</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="6" t="n"/>
     </row>
@@ -16335,6 +16385,42 @@
       <c r="H51" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>开机默认 PL 切片 (含合入 D13), CPU 切片只留退路</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>8;7</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>task/d18-pl-default</t>
         </is>
       </c>
     </row>

--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -15,7 +15,7 @@
     <sheet name="历史记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -232,10 +232,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2997,12 +2997,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$294</f>
+              <f>'指标趋势'!$A$294:$A$295</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$294</f>
+              <f>'指标趋势'!$B$294:$B$295</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3123,7 +3123,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46309"/>
-          <min val="46307"/>
+          <min val="46308"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3615,12 +3615,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$328</f>
+              <f>'指标趋势'!$A$328:$A$329</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$328</f>
+              <f>'指标趋势'!$B$328:$B$329</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -3741,7 +3741,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46309"/>
-          <min val="46307"/>
+          <min val="46308"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -8264,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8335,16 +8335,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>27/37</t>
+          <t>28/37</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 18/25 + 交付 9/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 18/25 + 交付 10/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>23/45</t>
+          <t>24/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 10/24 + 交付 13/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 10/24 + 交付 14/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8399,29 +8399,29 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.4489795918367347</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>22/49</t>
+          <t>23/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 9/24 + 交付 13/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 9/24 + 交付 14/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.7297</v>
+        <v>0.7568</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.5111</v>
+        <v>0.5333</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.449</v>
+        <v>0.4694</v>
       </c>
     </row>
     <row r="8">
@@ -8539,98 +8539,98 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>KR8.1</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>变差</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>上电到 0° 片亮起 (停转) (s, 越小越好)</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>15.8 (10-13) → 17.2</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>12 / 12 / 12；dr1v90 task/d18-pl-default d35c6d4 (上板 3 次重启 17.17–17.30 s)</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>变好</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>按名字找到板子 (s, 越小越好)</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>25.6 (10-13) → 24.4</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>20 / 20 / 20；dr1v90 task/d18-pl-default d35c6d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>阶段出口清单 — V0 出口  (已打勾 4/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>①2047 PL 切片上板通过</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>D2 (1/1)</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>②主机实时推流 15 fps</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>D1 (1/1)</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>③几何更正 + 镜像已核实</t>
+          <t>①2047 PL 切片上板通过</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>KR5.2 (1/1)</t>
+          <t>D2 (1/1)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -8657,22 +8657,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
+          <t>②主机实时推流 15 fps</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>KR8.1;KR8.2;D13 (0/3)</t>
+          <t>D1 (1/1)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -8684,22 +8684,22 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
+          <t>③几何更正 + 镜像已核实</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>D7;KR9.1;KR9.2 (0/3)</t>
+          <t>KR5.2 (1/1)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>⑥软件链路无人值守 ≥8 h</t>
+          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>KR7.2 (0/1)</t>
+          <t>KR8.1;KR8.2;D13 (0/3)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -8738,7 +8738,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>D15 (0/1)</t>
+          <t>D7;KR9.1;KR9.2 (0/3)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -8765,137 +8765,137 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>⑥软件链路无人值守 ≥8 h</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>KR7.2 (0/1)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>D15 (0/1)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>⑧内容 ≥2 + 一种交互</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>KR10.1;KR10.2 (2/2)</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>阶段出口清单 — V1 回板当天就绪  (已打勾 3/11；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>D10 (0/1)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>②桥 1 期 6 链 24 Hz 位流</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>D5 (1/1)</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>③桥接收 + 1.2G PRBS 测试件</t>
+          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>D4 (1/1)</t>
+          <t>D10 (0/1)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -8907,7 +8907,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>④1 期几何 LUT + 校准工具</t>
+          <t>②桥 1 期 6 链 24 Hz 位流</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>D6 (1/1)</t>
+          <t>D5 (1/1)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -8934,22 +8934,22 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
+          <t>③桥接收 + 1.2G PRBS 测试件</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>D8 (0/1)</t>
+          <t>D4 (1/1)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -8961,22 +8961,22 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>⑥全链路系统仿真</t>
+          <t>④1 期几何 LUT + 校准工具</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>D9 (0/1)</t>
+          <t>D6 (1/1)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -8998,12 +8998,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>⑦C1 台架逐像素 0 错</t>
+          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>D11 (0/1)</t>
+          <t>D8 (0/1)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -9015,7 +9015,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>⑧整机回板点亮步骤 + 一键脚本</t>
+          <t>⑥全链路系统仿真</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D9 (0/1)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -9042,7 +9042,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+          <t>⑦C1 台架逐像素 0 错</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D11 (0/1)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -9069,7 +9069,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>⑩面板映射 4 项信息到位</t>
+          <t>⑧整机回板点亮步骤 + 一键脚本</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -9096,425 +9096,429 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>⑩面板映射 4 项信息到位</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>⑪无串口运维可用</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>D7 (0/1)</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>风险表 (risks.csv；红 = 开，黄 = 监控，绿 = 关)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>影响 / 应对</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>负责 · 登记日期 · 来源</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>1.2G 可能过不了</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
 应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>影响：时钟偏差会丢帧
 应对：退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E44" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>影响：每块下半屏黑
 应对：硬件确认并补 0Ω</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>2260 从未收到合法 ACK（疑物理通路）</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>影响：1 期显示可能起不来
 应对：验证板一颗一组针对此问题，回板验证</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>影响：2 期 32 bit 像素带宽不够
 应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>WiFi/主机负载造成延迟尾巴（10-13 晚 p99 334 ms）</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>影响：延迟抖动超标
 应对：演示时停重任务；后续增量帧</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>影响：高速下接触不良/脱落
 应对：T2 板留 eMMC、打胶</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>D 盘 EIO（IP-guard 驱动）</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>影响：构建/提交偶发失败
 应对：看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>1 期面板映射缺 4 项信息</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>影响：1 期桥表无法定稿
 应对：问硬件同事</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>每日流水 (daily_log.csv，按天倒序)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>dr1v90 fdb4de6</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -9522,24 +9526,24 @@
       <c r="A56" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -9547,24 +9551,24 @@
       <c r="A57" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -9572,24 +9576,24 @@
       <c r="A58" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -9604,17 +9608,17 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -9622,24 +9626,24 @@
       <c r="A60" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -9647,9 +9651,9 @@
       <c r="A61" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -9659,12 +9663,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -9672,24 +9676,24 @@
       <c r="A62" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -9697,24 +9701,24 @@
       <c r="A63" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9722,24 +9726,24 @@
       <c r="A64" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -9747,24 +9751,24 @@
       <c r="A65" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -9779,17 +9783,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9797,80 +9801,80 @@
       <c r="A67" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B67" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B68" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
@@ -9879,17 +9883,17 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
@@ -9897,24 +9901,24 @@
       <c r="A71" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9924,22 +9928,22 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9947,24 +9951,24 @@
       <c r="A73" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -9972,24 +9976,24 @@
       <c r="A74" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10004,17 +10008,17 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10022,19 +10026,19 @@
       <c r="A76" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -10047,24 +10051,24 @@
       <c r="A77" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10079,17 +10083,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10097,19 +10101,19 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -10122,24 +10126,24 @@
       <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10154,17 +10158,17 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10172,19 +10176,19 @@
       <c r="A82" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="15" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -10197,24 +10201,24 @@
       <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10222,19 +10226,19 @@
       <c r="A84" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -10247,24 +10251,24 @@
       <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10279,17 +10283,17 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10297,24 +10301,24 @@
       <c r="A87" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10322,24 +10326,24 @@
       <c r="A88" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B88" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10347,20 +10351,24 @@
       <c r="A89" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr"/>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10368,20 +10376,24 @@
       <c r="A90" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr"/>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10394,15 +10406,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10415,19 +10431,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C92" s="7" t="inlineStr"/>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10435,24 +10447,20 @@
       <c r="A93" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10465,19 +10473,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>D12;D13;D14</t>
-        </is>
-      </c>
+      <c r="C94" s="7" t="inlineStr"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10492,12 +10496,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -10517,12 +10521,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -10542,17 +10546,17 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10560,19 +10564,19 @@
       <c r="A98" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -10585,18 +10589,93 @@
       <c r="A99" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B99" s="21" t="inlineStr">
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>D15;D16</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B102" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr"/>
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -11910,10 +11989,10 @@
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -11936,11 +12015,11 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217 (d13_boot/runs/levers, 串口真实复位时刻)</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4 (上板 3 次重启 17.17–17.30 s)</t>
         </is>
       </c>
       <c r="Q22" s="23" t="n">
-        <v>0.7594936708860759</v>
+        <v>0.6976744186046512</v>
       </c>
     </row>
     <row r="23">
@@ -12020,10 +12099,10 @@
         </is>
       </c>
       <c r="I24" s="6" t="n">
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -12046,11 +12125,11 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
       <c r="Q24" s="23" t="n">
-        <v>0.78125</v>
+        <v>0.819672131147541</v>
       </c>
     </row>
     <row r="25">
@@ -12420,7 +12499,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -14455,25 +14534,32 @@
       </c>
       <c r="C294" s="6" t="n"/>
       <c r="D294" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E294" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F294" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>12</v>
       </c>
       <c r="H294" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I294" s="6" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="295">
+      <c r="A295" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B295" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C295" s="6" t="n"/>
       <c r="D295" s="8" t="n">
         <v>46309</v>
       </c>
@@ -14589,25 +14675,32 @@
       </c>
       <c r="C328" s="6" t="n"/>
       <c r="D328" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E328" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F328" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>20</v>
       </c>
       <c r="H328" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I328" s="6" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="329">
+      <c r="A329" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B329" s="6" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="C329" s="6" t="n"/>
       <c r="D329" s="8" t="n">
         <v>46309</v>
       </c>
@@ -15226,7 +15319,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -16140,7 +16233,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>fdbb217 已装板: 亮起 15.8 s / 找板 25.6 s; 第二步 (写启动文件) 待用户批准</t>
+          <t>已随 D18 合主线 (启动提速+启动屏显); 第二步 (uboot.env/uInitrd) 待用户批准</t>
         </is>
       </c>
     </row>
@@ -16412,15 +16505,17 @@
       <c r="E52" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F52" s="19" t="n"/>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F52" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>task/d18-pl-default</t>
+          <t>合主线 (d35c6d4; 离线 15/15 + 上板 32/32)</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19446,8 +19541,90 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>KR8.1</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>上电到 0° 片亮起 (停转)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 task/d18-pl-default d35c6d4 (上板 3 次重启 17.17–17.30 s)</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>PL 默认开机 (多加载 PL 位流), 从 reboot 命令算</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>PL 默认开机找板 24.4–28.3 s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I70"/>
+  <autoFilter ref="A1:I72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -15,7 +15,7 @@
     <sheet name="历史记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -231,14 +231,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -8335,16 +8335,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>28/37</t>
+          <t>29/37</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 18/25 + 交付 10/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 19/25 + 交付 10/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>24/45</t>
+          <t>25/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 10/24 + 交付 14/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 11/24 + 交付 14/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8399,29 +8399,29 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>23/49</t>
+          <t>24/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 9/24 + 交付 14/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 10/24 + 交付 14/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.7568</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.5333</v>
+        <v>0.5556</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.4694</v>
+        <v>0.4898</v>
       </c>
     </row>
     <row r="8">
@@ -8540,29 +8540,29 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>KR8.1</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>变差</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>变好</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>上电到 0° 片亮起 (停转) (s, 越小越好)</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>15.8 (10-13) → 17.2</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>12 / 12 / 12；dr1v90 task/d18-pl-default d35c6d4 (上板 3 次重启 17.17–17.30 s)</t>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>15.8 (10-13) → 12.4</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>12 / 12 / 12；dr1v90 d13_boot/runs/20261014_145507 (串口 3 次)</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>25.6 (10-13) → 24.4</t>
+          <t>25.6 (10-13) → 19.8</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>20 / 20 / 20；dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>20 / 20 / 20；dr1v90 d13_boot/runs/20261014_145507</t>
         </is>
       </c>
     </row>
@@ -8714,9 +8714,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>🔄</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>KR8.1;KR8.2;D13 (0/3)</t>
+          <t>KR8.1;KR8.2;D13 (1/3)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -9219,30 +9219,30 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>1.2G 可能过不了</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
 应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
@@ -9275,18 +9275,18 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>影响：每块下半屏黑
 应对：硬件确认并补 0Ω</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
@@ -9303,18 +9303,18 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>2260 从未收到合法 ACK（疑物理通路）</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>影响：1 期显示可能起不来
 应对：验证板一颗一组针对此问题，回板验证</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
@@ -9331,18 +9331,18 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>影响：2 期 32 bit 像素带宽不够
 应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
@@ -9359,30 +9359,30 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
@@ -9415,30 +9415,30 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>影响：高速下接触不良/脱落
 应对：T2 板留 eMMC、打胶</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
@@ -9471,18 +9471,18 @@
           <t>开</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>1 期面板映射缺 4 项信息</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>影响：1 期桥表无法定稿
 应对：问硬件同事</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
@@ -9576,7 +9576,7 @@
       <c r="A58" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9601,7 +9601,7 @@
       <c r="A59" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9651,7 +9651,7 @@
       <c r="A61" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9726,7 +9726,7 @@
       <c r="A64" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9976,7 +9976,7 @@
       <c r="A74" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -10101,7 +10101,7 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="17" t="inlineStr">
+      <c r="B79" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -10126,7 +10126,7 @@
       <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="17" t="inlineStr">
+      <c r="B80" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -10276,7 +10276,7 @@
       <c r="A86" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B86" s="17" t="inlineStr">
+      <c r="B86" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -10351,7 +10351,7 @@
       <c r="A89" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="17" t="inlineStr">
+      <c r="B89" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -10639,7 +10639,7 @@
       <c r="A101" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="17" t="inlineStr">
+      <c r="B101" s="15" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -11786,7 +11786,7 @@
           <t>稳定</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11890,7 +11890,7 @@
       <c r="N20" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="O20" s="17" t="inlineStr">
+      <c r="O20" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11963,7 +11963,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>17.2</v>
+        <v>12.4</v>
       </c>
       <c r="J22" s="19" t="n">
         <v>46309</v>
@@ -12008,18 +12008,18 @@
       <c r="N22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="O22" s="17" t="inlineStr">
+      <c r="O22" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4 (上板 3 次重启 17.17–17.30 s)</t>
+          <t>dr1v90 d13_boot/runs/20261014_145507 (串口 3 次)</t>
         </is>
       </c>
       <c r="Q22" s="23" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.9677419354838709</v>
       </c>
     </row>
     <row r="23">
@@ -12061,7 +12061,7 @@
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="O23" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="I24" s="6" t="n">
-        <v>24.4</v>
+        <v>19.8</v>
       </c>
       <c r="J24" s="19" t="n">
         <v>46309</v>
@@ -12118,18 +12118,18 @@
       <c r="N24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="O24" s="17" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>dr1v90 d13_boot/runs/20261014_145507</t>
         </is>
       </c>
       <c r="Q24" s="23" t="n">
-        <v>0.819672131147541</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -12205,7 +12205,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -12250,7 +12250,7 @@
       <c r="N26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="17" t="inlineStr">
+      <c r="O26" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12309,7 +12309,7 @@
       <c r="N27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="17" t="inlineStr">
+      <c r="O27" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12475,7 +12475,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -14557,7 +14557,7 @@
         <v>46309</v>
       </c>
       <c r="B295" s="6" t="n">
-        <v>17.2</v>
+        <v>12.4</v>
       </c>
       <c r="C295" s="6" t="n"/>
       <c r="D295" s="8" t="n">
@@ -14698,7 +14698,7 @@
         <v>46309</v>
       </c>
       <c r="B329" s="6" t="n">
-        <v>24.4</v>
+        <v>19.8</v>
       </c>
       <c r="C329" s="6" t="n"/>
       <c r="D329" s="8" t="n">
@@ -16010,7 +16010,7 @@
         <v>46312</v>
       </c>
       <c r="F38" s="19" t="n"/>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16190,7 +16190,7 @@
         <v>46310</v>
       </c>
       <c r="F43" s="19" t="n"/>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16226,7 +16226,7 @@
         <v>46311</v>
       </c>
       <c r="F44" s="19" t="n"/>
-      <c r="G44" s="17" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16262,7 +16262,7 @@
         <v>46311</v>
       </c>
       <c r="F45" s="19" t="n"/>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16298,7 +16298,7 @@
         <v>46312</v>
       </c>
       <c r="F46" s="19" t="n"/>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16334,7 +16334,7 @@
         <v>46312</v>
       </c>
       <c r="F47" s="19" t="n"/>
-      <c r="G47" s="17" t="inlineStr">
+      <c r="G47" s="15" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16651,7 +16651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19591,40 +19591,122 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
+          <t>KR8.1</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>上电到 0° 片亮起 (停转)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 d13_boot/runs/20261014_145507 (串口 3 次)</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>D13 第二步后 (bootdelay 0 + 精简 uInitrd) + PL 默认开机</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
           <t>KR8.2</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>按名字找到板子</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F73" s="7" t="n">
         <v>24.4</v>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>V0 2047</t>
         </is>
       </c>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>PL 默认开机找板 24.4–28.3 s</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>KR8.2</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>按名字找到板子</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 d13_boot/runs/20261014_145507</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>3 次 19.8/20.3/20.9 s</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I72"/>
+  <autoFilter ref="A1:I74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -231,14 +231,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -8264,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8335,16 +8335,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.8378378378378378</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>29/37</t>
+          <t>31/37</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 19/25 + 交付 10/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 20/25 + 交付 11/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>25/45</t>
+          <t>27/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 11/24 + 交付 14/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 12/24 + 交付 15/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8399,29 +8399,29 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.4897959183673469</v>
+        <v>0.5306122448979592</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>24/49</t>
+          <t>26/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 10/24 + 交付 14/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 11/24 + 交付 15/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.8378</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.5556</v>
+        <v>0.6</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.4898</v>
+        <v>0.5306</v>
       </c>
     </row>
     <row r="8">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>12 / 12 / 12；dr1v90 d13_boot/runs/20261014_145507 (串口 3 次)</t>
+          <t>12.5 / 12.5 / 12.5；dr1v90 d13_boot/runs/20261014_145507 (串口 3 次)</t>
         </is>
       </c>
     </row>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>20 / 20 / 20；dr1v90 d13_boot/runs/20261014_145507</t>
+          <t>21 / 21 / 21；dr1v90 d13_boot/runs/20261014_145507</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>阶段出口清单 — V0 出口  (已打勾 4/8；状态由关联项在当日是否完成/达标推出)</t>
+          <t>阶段出口清单 — V0 出口  (已打勾 5/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
@@ -8714,9 +8714,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>KR8.1;KR8.2;D13 (1/3)</t>
+          <t>KR8.1;KR8.2;D13 (3/3)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -9209,40 +9209,40 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>1.2G 可能过不了</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
 应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
@@ -9265,124 +9265,124 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>影响：每块下半屏黑
 应对：硬件确认并补 0Ω</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>2260 从未收到合法 ACK（疑物理通路）</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>影响：1 期显示可能起不来
 应对：验证板一颗一组针对此问题，回板验证</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>影响：2 期 32 bit 像素带宽不够
 应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
@@ -9405,40 +9405,40 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>影响：高速下接触不良/脱落
 应对：T2 板留 eMMC、打胶</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
@@ -9461,28 +9461,28 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>1 期面板映射缺 4 项信息</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>影响：1 期桥表无法定稿
 应对：问硬件同事</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
@@ -9551,7 +9551,7 @@
       <c r="A57" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
@@ -9576,7 +9576,7 @@
       <c r="A58" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9601,7 +9601,7 @@
       <c r="A59" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9651,7 +9651,7 @@
       <c r="A61" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9676,7 +9676,7 @@
       <c r="A62" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>复验退回</t>
         </is>
@@ -9726,7 +9726,7 @@
       <c r="A64" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -9899,26 +9899,26 @@
     </row>
     <row r="71">
       <c r="A71" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
@@ -9933,17 +9933,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -9958,17 +9958,17 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -9976,9 +9976,9 @@
       <c r="A74" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10001,9 +10001,9 @@
       <c r="A75" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10026,24 +10026,24 @@
       <c r="A76" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10051,9 +10051,9 @@
       <c r="A77" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10083,17 +10083,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10101,9 +10101,9 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -10151,24 +10151,24 @@
       <c r="A81" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10176,24 +10176,24 @@
       <c r="A82" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B82" s="16" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10201,24 +10201,24 @@
       <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10233,17 +10233,17 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10251,19 +10251,19 @@
       <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="16" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10301,24 +10301,24 @@
       <c r="A87" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="16" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10326,9 +10326,9 @@
       <c r="A88" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10351,9 +10351,9 @@
       <c r="A89" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10376,24 +10376,24 @@
       <c r="A90" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10401,24 +10401,24 @@
       <c r="A91" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10431,15 +10431,19 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr"/>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10447,15 +10451,15 @@
       <c r="A93" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr"/>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -10468,20 +10472,20 @@
       <c r="A94" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B94" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr"/>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10494,19 +10498,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="C95" s="7" t="inlineStr"/>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10521,12 +10521,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
@@ -10621,17 +10621,17 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10639,24 +10639,24 @@
       <c r="A101" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>KR5.2</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 49031f6</t>
         </is>
       </c>
     </row>
@@ -10664,18 +10664,43 @@
       <c r="A102" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="21" t="inlineStr">
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B103" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr"/>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr"/>
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -11786,7 +11811,7 @@
           <t>稳定</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -11890,7 +11915,7 @@
       <c r="N20" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="O20" s="15" t="inlineStr">
+      <c r="O20" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -11963,7 +11988,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -12000,17 +12025,17 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="O22" s="15" t="inlineStr">
-        <is>
-          <t>🔄</t>
+        <v>12.5</v>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -12019,7 +12044,7 @@
         </is>
       </c>
       <c r="Q22" s="23" t="n">
-        <v>0.9677419354838709</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -12061,7 +12086,7 @@
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="15" t="inlineStr">
+      <c r="O23" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12110,13 +12135,13 @@
         </is>
       </c>
       <c r="L24" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
@@ -12205,7 +12230,7 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>🔄 进行中 / 未达标</t>
         </is>
@@ -12250,7 +12275,7 @@
       <c r="N26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="15" t="inlineStr">
+      <c r="O26" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12309,7 +12334,7 @@
       <c r="N27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="15" t="inlineStr">
+      <c r="O27" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12475,7 +12500,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -12499,7 +12524,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -14537,19 +14562,19 @@
         <v>46308</v>
       </c>
       <c r="E294" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="F294" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="G294" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H294" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="I294" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="295">
@@ -14564,19 +14589,19 @@
         <v>46309</v>
       </c>
       <c r="E295" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="F295" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="G295" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H295" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="I295" s="6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="309">
@@ -14678,19 +14703,19 @@
         <v>46308</v>
       </c>
       <c r="E328" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F328" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="G328" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H328" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="I328" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="329">
@@ -14705,19 +14730,19 @@
         <v>46309</v>
       </c>
       <c r="E329" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F329" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="G329" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H329" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="I329" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="343">
@@ -15319,7 +15344,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -16010,7 +16035,7 @@
         <v>46312</v>
       </c>
       <c r="F38" s="19" t="n"/>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16190,7 +16215,7 @@
         <v>46310</v>
       </c>
       <c r="F43" s="19" t="n"/>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G43" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16225,15 +16250,17 @@
       <c r="E44" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F44" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>已随 D18 合主线 (启动提速+启动屏显); 第二步 (uboot.env/uInitrd) 待用户批准</t>
+          <t>随 D18 合主线; 第二步已装卡 (uboot.env+精简 uInitrd), 亮起 12.4 s / 找板 ≤20.9 s</t>
         </is>
       </c>
     </row>
@@ -16262,7 +16289,7 @@
         <v>46311</v>
       </c>
       <c r="F45" s="19" t="n"/>
-      <c r="G45" s="15" t="inlineStr">
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16298,7 +16325,7 @@
         <v>46312</v>
       </c>
       <c r="F46" s="19" t="n"/>
-      <c r="G46" s="15" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
@@ -16334,7 +16361,7 @@
         <v>46312</v>
       </c>
       <c r="F47" s="19" t="n"/>
-      <c r="G47" s="15" t="inlineStr">
+      <c r="G47" s="17" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>

--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -15,7 +15,7 @@
     <sheet name="历史记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'历史记录'!$A$1:$I$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4099,12 +4099,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$362</f>
+              <f>'指标趋势'!$A$362:$A$363</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$362</f>
+              <f>'指标趋势'!$B$362:$B$363</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4225,7 +4225,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46309"/>
-          <min val="46307"/>
+          <min val="46308"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -4341,12 +4341,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'指标趋势'!$A$379</f>
+              <f>'指标趋势'!$A$379:$A$380</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'指标趋势'!$B$379</f>
+              <f>'指标趋势'!$B$379:$B$380</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -4467,7 +4467,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="46309"/>
-          <min val="46307"/>
+          <min val="46308"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -8264,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8335,16 +8335,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.8378378378378378</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>31/37</t>
+          <t>34/37</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>KR 20/25 + 交付 11/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
+          <t>KR 22/25 + 交付 12/12 — 统一口径：达成率_P = (P 目标已达标的 KR 数 + P 需要的交付里已完成数) ÷ (有 P 目标的 KR 数 + P 需要的交付总数)，P = V0 / V1 / V2。</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>27/45</t>
+          <t>30/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 12/24 + 交付 15/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 14/24 + 交付 16/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8399,29 +8399,29 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.5306122448979592</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>26/49</t>
+          <t>29/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 11/24 + 交付 15/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 13/24 + 交付 16/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.8378</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.5306</v>
+        <v>0.5918</v>
       </c>
     </row>
     <row r="8">
@@ -8593,98 +8593,98 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>变好</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用) (是/否, 越大越好)</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>0 (10-13) → 1</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1 / 1；dr1v90 dee9be6</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>阶段出口清单 — V0 出口  (已打勾 5/8；状态由关联项在当日是否完成/达标推出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>KR9.2</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>变好</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>远程升级失败自动回滚 (1=有) (是/否, 越大越好)</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>0 (10-13) → 1</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1 / 1；dr1v90 dee9be6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>阶段出口清单 — V0 出口  (已打勾 6/8；状态由关联项在当日是否完成/达标推出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>①2047 PL 切片上板通过</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>D2 (1/1)</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>②主机实时推流 15 fps</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>D1 (1/1)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>③几何更正 + 镜像已核实</t>
+          <t>①2047 PL 切片上板通过</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>KR5.2 (1/1)</t>
+          <t>D2 (1/1)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
+          <t>②主机实时推流 15 fps</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>KR8.1;KR8.2;D13 (3/3)</t>
+          <t>D1 (1/1)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -8738,22 +8738,22 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
+          <t>③几何更正 + 镜像已核实</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>D7;KR9.1;KR9.2 (0/3)</t>
+          <t>KR5.2 (1/1)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -8765,22 +8765,22 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>⑥软件链路无人值守 ≥8 h</t>
+          <t>④复位到亮起 ≤12 s、找板 ≤20 s</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>KR7.2 (0/1)</t>
+          <t>KR8.1;KR8.2;D13 (3/3)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -8792,22 +8792,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+          <t>⑤无串口远程运维：遥测 + 升级失败自动回滚</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>D15 (0/1)</t>
+          <t>D7;KR9.1;KR9.2 (3/3)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -8819,137 +8819,137 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>⑥软件链路无人值守 ≥8 h</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>KR7.2 (0/1)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>⑦WiFi 端 12-bit 通路在 2047 上跑通</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>D15 (0/1)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>⑧内容 ≥2 + 一种交互</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>KR10.1;KR10.2 (2/2)</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 3/11；状态由关联项在当日是否完成/达标推出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>阶段出口清单 — V1 回板当天就绪  (已打勾 4/11；状态由关联项在当日是否完成/达标推出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>条目</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>关联项进度</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>D10 (0/1)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>②桥 1 期 6 链 24 Hz 位流</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>D5 (1/1)</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>③桥接收 + 1.2G PRBS 测试件</t>
+          <t>①主控 1 期整合位流 (PL 切片 + 12-bit 上行，V3 引脚)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>D4 (1/1)</t>
+          <t>D10 (0/1)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -8961,7 +8961,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>④1 期几何 LUT + 校准工具</t>
+          <t>②桥 1 期 6 链 24 Hz 位流</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>D6 (1/1)</t>
+          <t>D5 (1/1)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -8988,22 +8988,22 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
+          <t>③桥接收 + 1.2G PRBS 测试件</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>D8 (0/1)</t>
+          <t>D4 (1/1)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -9015,22 +9015,22 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>⑥全链路系统仿真</t>
+          <t>④1 期几何 LUT + 校准工具</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>D9 (0/1)</t>
+          <t>D6 (1/1)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -9042,7 +9042,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>⑦C1 台架逐像素 0 错</t>
+          <t>⑤主控↔桥↔2260 联合仿真 0 错</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>D11 (0/1)</t>
+          <t>D8 (0/1)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -9069,7 +9069,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>⑧整机回板点亮步骤 + 一键脚本</t>
+          <t>⑥全链路系统仿真</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D9 (0/1)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -9096,7 +9096,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+          <t>⑦C1 台架逐像素 0 错</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>人工状态</t>
+          <t>D11 (0/1)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -9123,7 +9123,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>⑩面板映射 4 项信息到位</t>
+          <t>⑧整机回板点亮步骤 + 一键脚本</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -9150,425 +9150,429 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>⑨硬件确认清单闭环：灯板 SDO→SDI 0Ω、CN3/CN6 n→n、R176–R181 等</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>⑩面板映射 4 项信息到位</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>人工状态</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>10-13 主会话规划</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>⑪无串口运维可用</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>D7 (0/1)</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>D7 (1/1)</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>风险表 (risks.csv；红 = 开，黄 = 监控，绿 = 关)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>影响 / 应对</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>负责 · 登记日期 · 来源</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>1.2G 可能过不了</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>影响：DR1 无 SERDES，09-22 DR1↔DR1 1.2G 全死
 应对：退路 1.0G × 16 lane；V1 回板 PRBS 实测定</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>主会话+硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>1 期 4,296 片/s 桥链路余量仅 0.40%</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>影响：时钟偏差会丢帧
 应对：退路降到 22 Hz（用户定保持 24 Hz）</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>灯板 SDO→SDI 0Ω 在 09-18 图上悬空</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>影响：每块下半屏黑
 应对：硬件确认并补 0Ω</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>2260 从未收到合法 ACK（疑物理通路）</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>影响：1 期显示可能起不来
 应对：验证板一颗一组针对此问题，回板验证</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>硬件+主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>2 期 DDR 带宽：16 bit 余量约 11%，32 bit 像素超限</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>影响：2 期 32 bit 像素带宽不够
 应对：B 线 T2 板 32 bit DDR + PL 读口 ≥200 MHz/分端口</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>偶发慢读 133 µs &gt; 30 Hz 片窗 110 µs</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>影响：偶发迟到掉片
 应对：D16 预取缓冲 + 降争用</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>WiFi/主机负载造成延迟尾巴（10-13 晚 p99 334 ms）</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>影响：延迟抖动超标
 应对：演示时停重任务；后续增量帧</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>转子离心 68–136 g：FS03 0.5 mm 板对板、TF 卡</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>影响：高速下接触不良/脱落
 应对：T2 板留 eMMC、打胶</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>监控</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>D 盘 EIO（IP-guard 驱动）</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="D53" s="18" t="inlineStr">
         <is>
           <t>影响：构建/提交偶发失败
 应对：看门狗自动重挂 + 构建放 WSL 本地盘</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E53" s="18" t="inlineStr">
         <is>
           <t>主会话 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>1 期面板映射缺 4 项信息</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>影响：1 期桥表无法定稿
 应对：问硬件同事</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>硬件 · 2026-10-13 · 10-13 主会话规划</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>每日流水 (daily_log.csv，按天倒序)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>上行出口全量复验 45/0, 合主线</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>dr1v90 fdb4de6</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -9576,24 +9580,24 @@
       <c r="A58" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
+          <t>上行出口全量复验 45/0, 合主线</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>dr1v90 fdb4de6</t>
         </is>
       </c>
     </row>
@@ -9601,24 +9605,24 @@
       <c r="A59" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
+          <t>PL 切片上板: 与 CPU 逐字节一致、30 min 无停摆, 但内容帧率 4.2&lt;15, 退回</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>project_ddr_budget_by_phase_1013</t>
+          <t>scratchpad/v_pls4_board.log</t>
         </is>
       </c>
     </row>
@@ -9626,24 +9630,24 @@
       <c r="A60" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
+          <t>30 Hz 带载迟到+掉片 3.7% (空载 0.2% 来自旧 netguard), 归因测试中</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>project_short_term_delivery_1013</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -9658,17 +9662,17 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
+          <t>纯切片带载约 21 min 停摆; 无负载浸泡 2×30 min 不停摆</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 debd3cd</t>
+          <t>project_ddr_budget_by_phase_1013</t>
         </is>
       </c>
     </row>
@@ -9676,24 +9680,24 @@
       <c r="A62" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
+          <t>用户定目标: 复位到亮起 ≤12 s, 找板 ≤20 s</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>scratchpad v_pls6_board.log</t>
+          <t>project_short_term_delivery_1013</t>
         </is>
       </c>
     </row>
@@ -9701,9 +9705,9 @@
       <c r="A63" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -9713,12 +9717,12 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
+          <t>找到 PL 切片器带载停摆根因: 零列描述符丢失 (公共核, 2260 也有) + pop 握手串片, 已修</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/pls-2047 debd3cd</t>
         </is>
       </c>
     </row>
@@ -9726,24 +9730,24 @@
       <c r="A64" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
+          <t>上板 60 min 带载 0 停摆、逐字节一致、late 0; 帧率 13.8 差 0.5 退回</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d16-ddr 539d303</t>
+          <t>scratchpad v_pls6_board.log</t>
         </is>
       </c>
     </row>
@@ -9751,24 +9755,24 @@
       <c r="A65" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B65" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
+          <t>2047 PL 实时切片上板全过: 60 min 带载 0 停摆, 帧率 15.0, 与 CPU 逐字节一致</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>feedback_save_weekly_quota</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9776,24 +9780,24 @@
       <c r="A66" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B66" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
+          <t>DDR 慢读根因: 每圈约 1/3 角度每取一列都换行, 两类 CPU 负载叠加越阈值 (0.002%→3%); 建议网格 4×4 分块</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/pls-2047 782e9e3</t>
+          <t>dr1v90 task/d16-ddr 539d303</t>
         </is>
       </c>
     </row>
@@ -9801,24 +9805,24 @@
       <c r="A67" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
+          <t>用户定: 子 agent 并行 ≤5 (周额度); 跑完的 agent 关掉</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 2364e5c</t>
+          <t>feedback_save_weekly_quota</t>
         </is>
       </c>
     </row>
@@ -9833,17 +9837,17 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>V0</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
+          <t>V0 出口清单: PL 切片上板通过 (D2) 可打勾</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>用户在场实转</t>
+          <t>dr1v90 task/pls-2047 782e9e3</t>
         </is>
       </c>
     </row>
@@ -9851,24 +9855,24 @@
       <c r="A69" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
+          <t>2047 PL 实时切片合进主线 (含公共核两处 bug 修复); D3 上行档位流需按新核重综合</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>用户 10-14</t>
+          <t>dr1v90 2364e5c</t>
         </is>
       </c>
     </row>
@@ -9876,24 +9880,24 @@
       <c r="A70" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+      <c r="B70" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
+          <t>PL 硬件切片首次实转上屏 (650 rpm, 完成率 100%, CPU 82% 空闲), 用户确认与 CPU 切片无区别</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d18-pl-default d35c6d4</t>
+          <t>用户在场实转</t>
         </is>
       </c>
     </row>
@@ -9908,12 +9912,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
+          <t>用户定: 只保留 PL 切片, 固化开机流程, CPU 切片只留应急退路</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9924,7 +9928,7 @@
     </row>
     <row r="72">
       <c r="A72" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
@@ -9933,48 +9937,48 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>开机默认 PL 切片合主线: 上电基础显示 → 推流显示推流 → 停推 5 min 回基础演示; CPU 只留应急退路</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 task/d18-pl-default d35c6d4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>用户定目标放宽: 亮起 ≤12.5 s / 找板 ≤21 s; V0 出口 ④ 达成</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>用户 10-14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
@@ -9983,42 +9987,42 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>无串口远程运维合主线: 升级坏包 (含断网包) 自动回滚后板子能按名字找回; 网络守护不再造成切片迟到 (旧版每分钟 2061 次 → 0); V0 出口 ⑤ 达成</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+        <v>46309</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>根因</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D15b</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>32 bit PL 全黑: 板端写 LUT 基址仍用 16 bit 布局偏移, PL 把网格当角度表读; 已修 308d1bb, 待上板</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 task/d15b-color-p2</t>
         </is>
       </c>
     </row>
@@ -10028,22 +10032,22 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10051,24 +10055,24 @@
       <c r="A77" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10078,22 +10082,22 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10101,24 +10105,24 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10126,24 +10130,24 @@
       <c r="A80" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10151,19 +10155,19 @@
       <c r="A81" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10183,17 +10187,17 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10201,24 +10205,24 @@
       <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10226,24 +10230,24 @@
       <c r="A84" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10251,19 +10255,19 @@
       <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -10276,24 +10280,24 @@
       <c r="A86" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10301,24 +10305,24 @@
       <c r="A87" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10326,24 +10330,24 @@
       <c r="A88" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B88" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10351,24 +10355,24 @@
       <c r="A89" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10376,19 +10380,19 @@
       <c r="A90" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -10401,24 +10405,24 @@
       <c r="A91" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10426,19 +10430,19 @@
       <c r="A92" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B92" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -10451,20 +10455,24 @@
       <c r="A93" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr"/>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10472,20 +10480,24 @@
       <c r="A94" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr"/>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10493,20 +10505,24 @@
       <c r="A95" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr"/>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10521,12 +10537,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D3;D4;D5</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -10544,19 +10560,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10564,24 +10576,20 @@
       <c r="A98" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>D12;D13;D14</t>
-        </is>
-      </c>
+      <c r="B98" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10594,19 +10602,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
+      <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10621,12 +10625,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -10646,17 +10650,17 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10664,19 +10668,19 @@
       <c r="A102" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -10689,18 +10693,118 @@
       <c r="A103" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B103" s="21" t="inlineStr">
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>D15;D16</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr"/>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -12230,9 +12334,9 @@
           <t>运维</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>🔄 进行中 / 未达标</t>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>✅ 达成当前期目标</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -12256,10 +12360,10 @@
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
@@ -12275,18 +12379,18 @@
       <c r="N26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="17" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
       <c r="Q26" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -12315,10 +12419,10 @@
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
@@ -12334,18 +12438,18 @@
       <c r="N27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="17" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/rotor-ops 05c4231</t>
+          <t>dr1v90 dee9be6</t>
         </is>
       </c>
       <c r="Q27" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -14909,25 +15013,32 @@
       </c>
       <c r="C362" s="6" t="n"/>
       <c r="D362" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E362" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F362" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G362" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H362" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I362" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="363">
+      <c r="A363" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B363" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" s="6" t="n"/>
       <c r="D363" s="8" t="n">
         <v>46309</v>
       </c>
@@ -15010,25 +15121,32 @@
       </c>
       <c r="C379" s="6" t="n"/>
       <c r="D379" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E379" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F379" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G379" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H379" s="8" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I379" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="380">
+      <c r="A380" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B380" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C380" s="6" t="n"/>
       <c r="D380" s="8" t="n">
         <v>46309</v>
       </c>
@@ -15344,7 +15462,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -16034,15 +16152,17 @@
       <c r="E38" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="F38" s="19" t="n"/>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F38" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>7ef55e1 离线过; 上板 V3 待补测 (agent 已关, 开新的接)</t>
+          <t>合主线 dee9be6 (D7/D7b/D7c; 新克隆上板 V3N 连续 3 次 11/11 + V2 12/12, 离线回归 84 过)</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19732,8 +19852,90 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>KR9.1</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>转子遥测可用 (1=可用)</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 dee9be6</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>povstat 遥测 + povnetd 状态上板可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>KR9.2</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>远程升级失败自动回滚 (1=有)</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>是/否</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>V0 2047</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 dee9be6</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>断网坏升级包连续 3 次自动回滚并按名字找回; 坏自检包回滚</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I74"/>
+  <autoFilter ref="A1:I76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/progress/显性目的进度_2026-10-14.xlsx
+++ b/docs/progress/显性目的进度_2026-10-14.xlsx
@@ -8264,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>30/45</t>
+          <t>31/45</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>KR 14/24 + 交付 16/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
+          <t>KR 14/24 + 交付 17/21 — 只按「必须」项计：KR 全算必须；交付看 deliverables.csv 的「级别」列 (必须/加分)，加分项不进分子分母。</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -8399,16 +8399,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.5918367346938775</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>29/49</t>
+          <t>30/49</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KR 13/24 + 交付 16/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
+          <t>KR 13/24 + 交付 17/25 — 交付的"需要"是嵌套的：V0 需要 = 阶段 V0；V1 需要 = V0 + V1准备；V2 需要 = V1 需要 + V2 (阶段列见 deliverables.csv，没填阶段的交付不计)。</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -8418,10 +8418,10 @@
         <v>0.9189000000000001</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0.6667</v>
+        <v>0.6889</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.5918</v>
+        <v>0.6122</v>
       </c>
     </row>
     <row r="8">
@@ -8650,7 +8650,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>阶段出口清单 — V0 出口  (已打勾 6/8；状态由关联项在当日是否完成/达标推出)</t>
+          <t>阶段出口清单 — V0 出口  (已打勾 7/8；状态由关联项在当日是否完成/达标推出)</t>
         </is>
       </c>
     </row>
@@ -8849,9 +8849,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>⬜</t>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>D15 (0/1)</t>
+          <t>D15 (1/1)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -10028,7 +10028,7 @@
     </row>
     <row r="76">
       <c r="A76" s="19" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
@@ -10037,42 +10037,42 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
+          <t>WiFi 端 12-bit 通路合主线: 32 bit 像素 PL/CPU 与 CPU 逐字节一致, 2047 上跑通; V0 出口 ⑦ 达成 (7/8)。已知限制: 32 bit 只到 10.83 rps (16.15 rps 时完成率 82-91%)</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 b0f6b5d</t>
+          <t>dr1v90 3a41eb7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>交付完成</t>
+        <v>46309</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>开始</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>KR7.2</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
+          <t>8 h 无人值守长跑开跑 19:20 (假转黑屏, 主线 voxslice 0.6 + 卡上 PL 默认; 推 40 min/停 7 min 循环; 判据 S1-S9; 15 min 试跑 9/9)</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 71d006f / 473abcf</t>
+          <t>dr1v90 26e69ec soak8h</t>
         </is>
       </c>
     </row>
@@ -10087,17 +10087,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
+          <t>按名字找板 (mDNS) 完成：无串口自重启后 34 s 按名字找到并 ssh 上</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 596b191</t>
+          <t>dr1v90 b0f6b5d</t>
         </is>
       </c>
     </row>
@@ -10105,24 +10105,24 @@
       <c r="A79" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
+          <t>纯切片 30 Hz 位流第一次上硅 D'0–D'3，尾部 late 0.2%，暂停 netguard 后 late/miss 为 0</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 60c619a / 596b191</t>
+          <t>dr1v90 71d006f / 473abcf</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>复验通过</t>
+          <t>交付完成</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
+          <t>主机实时推流完成：10 分钟 15.0 fps，NAK 0 / forced 0</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 9bf16ad</t>
+          <t>dr1v90 596b191</t>
         </is>
       </c>
     </row>
@@ -10155,24 +10155,24 @@
       <c r="A81" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
+          <t>第一次上板端到端延迟 p50 114 ms 未过（停等发送），改发送流水线后降到 84.7 ms</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 60c619a / 596b191</t>
         </is>
       </c>
     </row>
@@ -10187,17 +10187,17 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
+          <t>主会话新克隆独立复验离线+上板全过，合主线（延迟 p50 95 ms / p99 236.6 ms）</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 6a373d3</t>
+          <t>dr1v90 9bf16ad</t>
         </is>
       </c>
     </row>
@@ -10205,24 +10205,24 @@
       <c r="A83" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
+          <t>桥接收核对 12-bit 第一次复验 FAIL（新克隆无可执行位），退回</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 cdf49c6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10230,24 +10230,24 @@
       <c r="A84" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
+          <t>桥接收核对 12-bit 复验 PASS，合主线</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 6a373d3</t>
         </is>
       </c>
     </row>
@@ -10255,9 +10255,9 @@
       <c r="A85" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -10267,12 +10267,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
+          <t>桥驱动 2260 1 期 6 链 24 Hz 12-bit 复验 ALL PASS，合主线</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 cdf49c6</t>
         </is>
       </c>
     </row>
@@ -10280,24 +10280,24 @@
       <c r="A86" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
+          <t>6 链 4296 片/s 能跑但余量仅 0.40%，瓶颈是桥→2260 链路；留 10% 需 ≤3921 片/s，待用户定</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 44ed2cd</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10305,19 +10305,19 @@
       <c r="A87" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B87" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
+          <t>发现 10-10 验证板 profile 寄存器在 166.67 MHz 下超规格（GCLK 667&gt;600），1 期表已改</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -10337,17 +10337,17 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
+          <t>几何 LUT 生成器逐字节复现 2047 s3lut，verify 22 PASS，合主线</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 ffbfeeb</t>
+          <t>dr1v90 44ed2cd</t>
         </is>
       </c>
     </row>
@@ -10355,19 +10355,19 @@
       <c r="A89" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
+          <t>转子运维首次复验 T5 偶发 FAIL，退回返工</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -10380,24 +10380,24 @@
       <c r="A90" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>复验退回</t>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
+          <t>10 类内容 + 手机网页遥控离线复验 ALL PASS，用户实转看过（尚未正式上板验收）</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>dr1v90 ffbfeeb</t>
         </is>
       </c>
     </row>
@@ -10405,24 +10405,24 @@
       <c r="A91" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
+          <t>2047 PL 切片离线复验 26/0，待上板（之后 9ba9af0 测试用例过时 26/27 待修）</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 764f81d</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
+          <t>延迟降低上板复验 FAIL：B1 翻页 14.39&lt;15 fps，p99 225 ms，退回</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -10455,24 +10455,24 @@
       <c r="A93" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B93" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
+          <t>第二次上板仍未过，根因晚间 WiFi 尾巴（p99 334 vs 白天 48 ms）；判据改为调度问题 0 + 网络晚到 ≤1%，明早主机空闲复测</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 task/d13-boot fdbb217</t>
+          <t>dr1v90 764f81d</t>
         </is>
       </c>
     </row>
@@ -10480,9 +10480,9 @@
       <c r="A94" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>复验退回</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
+          <t>启动提速上板 FAIL 11 项，但改进已装板保留（6 次重启正常），退回继续压启动时间</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -10505,24 +10505,24 @@
       <c r="A95" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>复验通过</t>
+      <c r="B95" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
+          <t>启动提速两轮后：复位→0° 片亮起 38.7→20.1→15.8 s，找板 34→30→25.6 s</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 1995be8</t>
+          <t>dr1v90 task/d13-boot fdbb217</t>
         </is>
       </c>
     </row>
@@ -10530,19 +10530,19 @@
       <c r="A96" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B96" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>D3;D4;D5</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
+          <t>第二步（bootdelay 0 / 精简 uInitrd）写启动文件被权限系统拒绝，需用户明早本人批准后执行</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -10555,20 +10555,24 @@
       <c r="A97" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B97" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr"/>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>复验通过</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
+          <t>WiFi 端 32 bit 像素（X2R10G10B10）阶段 1 复验：黄金/PL 仿真一致，合主线</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>dr1v90 1995be8</t>
         </is>
       </c>
     </row>
@@ -10576,20 +10580,24 @@
       <c r="A98" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B98" s="21" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr"/>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>D3;D4;D5</t>
+        </is>
+      </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
+          <t>下午用户：2260 相关先暂停、先做共用部分（token 不够）；15:00 又改为多开并行恢复 2260</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_sw_three_phases_1013.md</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10613,12 @@
       <c r="C99" s="7" t="inlineStr"/>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
+          <t>软件三期：0 期 2047 屏（现在）/ 1 期 2260 验证板 160×180（预计 11-10 回板）/ 2 期 192×216 目标板；1 期目标 24 Hz / 358 片 / 6 链</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_arch_common_front_display_backend.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10618,24 +10626,20 @@
       <c r="A100" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B100" s="20" t="inlineStr">
-        <is>
-          <t>决定</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="B100" s="21" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
+          <t>硬件 1 期验证板预计 2026-11-10 回板（初步交期，可能变），回板前软件能做的都前置</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_sw_three_phases_1013.md</t>
         </is>
       </c>
     </row>
@@ -10648,19 +10652,15 @@
           <t>决定</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+      <c r="C101" s="7" t="inlineStr"/>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
+          <t>架构切分：PL 切片器及之前为各期共用的公共部分，屏幕显示为可替换后端，两者之间用实时按角度片流接口</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>claude_memory/project_short_term_delivery_1013.md</t>
+          <t>claude_memory/project_arch_common_front_display_backend.md</t>
         </is>
       </c>
     </row>
@@ -10675,12 +10675,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>D12;D13;D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
+          <t>用户定：2 期上行 1.2G；1 期保持 24 Hz（358 片，桥链路余量 0.40%）不降档</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
+          <t>傍晚用户：杜邦线跑不了 1.2G，1.2G 实测等 V1 回板；C1 台架只做 ≤300M 低速功能档</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D15;D16</t>
+          <t>D12;D13;D14</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
+          <t>19:00 用户：V0 可见的先插队、V1 接着做，新派 D12 延迟降低 / D13 启动提速 / D14 内容与手机控制</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -10750,17 +10750,17 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>KR5.2</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+          <t>21:10 用户定 D13 目标：复位到 0° 片亮起 ≤12 s，找板 ≤20 s（看板 KR8.1 已改）</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>dr1v90 49031f6</t>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
         </is>
       </c>
     </row>
@@ -10768,19 +10768,19 @@
       <c r="A106" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>问题</t>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D15;D16</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+          <t>用户选 12-bit 方案 A：WiFi 端传高位宽、像素位宽 16/32 bit 可配（D15）；DDR 做到极限 A 线（D16），B 线并入 T2 硬件</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -10793,18 +10793,68 @@
       <c r="A107" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>KR5.2</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>用户实转核实：2047 旧表镜像，已更正为新表 0decad54</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>dr1v90 49031f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>D7 上板补测会装/还原 autorun，冲掉 D13 补丁，须排在 D13 定稿合并之后；夜间板子排程 D12→D13→D2→D7→8 h 长跑</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>claude_memory/project_short_term_delivery_1013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr"/>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr"/>
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>显性目的进度看板第一版建立：10 个显性目的 + KR 趋势 + 燃起图 + 里程碑趋势</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>claude_memory/project_progress_dashboard.md</t>
         </is>
@@ -15462,7 +15512,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -16444,15 +16494,17 @@
       <c r="E46" s="19" t="n">
         <v>46312</v>
       </c>
-      <c r="F46" s="19" t="n"/>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>🔄</t>
+      <c r="F46" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>阶段 1 合主线 1995be8; 阶段 2 待 D2 合主线后开新 agent</t>
+          <t>阶段 1 1995be8 + 阶段 2 合主线 3a41eb7 (上板: 32/16 bit PL==CPU 逐字节; 32 bit 推流 PL @10.83 rps 完成率 100%; 回归 0808333)</t>
         </is>
       </c>
     </row>
